--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -1229,30 +1229,30 @@
         </is>
       </c>
       <c r="C3" s="23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="53" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="F3" s="23" t="n">
         <v>128</v>
       </c>
       <c r="G3" s="23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H3" s="53" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="I3" s="23" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/12</t>
         </is>
       </c>
       <c r="J3" s="23" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L3" s="53" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="M3" s="27" t="inlineStr">
@@ -1302,11 +1302,11 @@
         <v>114</v>
       </c>
       <c r="G4" s="23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="53" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="I4" s="23" t="inlineStr">
@@ -1324,9 +1324,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L4" s="53" t="inlineStr">
-        <is>
-          <t>43%</t>
+      <c r="L4" s="65" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="M4" s="27" t="inlineStr">
@@ -1361,16 +1361,16 @@
         <v>106</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H5" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">
@@ -1383,9 +1383,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L5" s="65" t="inlineStr">
+        <is>
+          <t>58%</t>
         </is>
       </c>
       <c r="M5" s="27" t="inlineStr">
@@ -1420,11 +1420,11 @@
         <v>10</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="53" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -1442,9 +1442,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L6" s="53" t="inlineStr">
-        <is>
-          <t>30%</t>
+      <c r="L6" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M6" s="27" t="inlineStr">
@@ -1501,9 +1501,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L7" s="53" t="inlineStr">
-        <is>
-          <t>23%</t>
+      <c r="L7" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M7" s="27" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L8" s="65" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="M8" s="27" t="inlineStr">
@@ -1597,11 +1597,11 @@
         <v>151</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H9" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -1619,9 +1619,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L9" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L9" s="65" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="M9" s="27" t="inlineStr">
@@ -1656,11 +1656,11 @@
         <v>75</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H10" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -1678,9 +1678,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L10" s="53" t="inlineStr">
-        <is>
-          <t>29%</t>
+      <c r="L10" s="65" t="inlineStr">
+        <is>
+          <t>52%</t>
         </is>
       </c>
       <c r="M10" s="27" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M11" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-08 00:00:00</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>151</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H12" s="53" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="L12" s="53" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M12" s="27" t="inlineStr">
@@ -1833,11 +1833,11 @@
         <v>116</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="L13" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M13" s="27" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="L14" s="53" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="M14" s="27" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="L15" s="53" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="M15" s="27" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="L16" s="53" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="M16" s="27" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="L17" s="53" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="M17" s="27" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="L18" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="M18" s="27" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="L19" s="53" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="M19" s="27" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="L20" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M20" s="27" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="L21" s="53" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="M21" s="27" t="inlineStr">
@@ -2364,11 +2364,11 @@
         <v>78</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="H22" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+        <v>42</v>
+      </c>
+      <c r="H22" s="65" t="inlineStr">
+        <is>
+          <t>54%</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>31/62</t>
+          <t>41/62</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -2386,9 +2386,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L22" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L22" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M22" s="27" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="L23" s="53" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="M23" s="27" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="L24" s="53" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="M24" s="27" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="L25" s="53" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="M25" s="27" t="inlineStr">
@@ -2659,11 +2659,11 @@
         <v>105</v>
       </c>
       <c r="G27" s="23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="53" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="L27" s="53" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M27" s="27" t="inlineStr">
@@ -3035,14 +3035,14 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L33" s="65" t="inlineStr">
-        <is>
-          <t>82%</t>
+      <c r="L33" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M33" s="27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-07 00:00:00</t>
         </is>
       </c>
     </row>
@@ -3533,11 +3533,11 @@
         <v>37</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E42" s="65" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="F42" s="23" t="n">
@@ -3684,9 +3684,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L44" s="65" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="L44" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M44" s="65" t="inlineStr">
@@ -3743,14 +3743,14 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L45" s="65" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="M45" s="27" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="L45" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M45" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -3839,11 +3839,11 @@
         <v>97</v>
       </c>
       <c r="G47" s="23" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H47" s="65" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="I47" s="23" t="inlineStr">
@@ -3861,9 +3861,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L47" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+      <c r="L47" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M47" s="67" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="L51" s="53" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M51" s="27" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="L52" s="53" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="M52" s="27" t="inlineStr">
@@ -4333,9 +4333,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L55" s="65" t="inlineStr">
-        <is>
-          <t>62%</t>
+      <c r="L55" s="53" t="inlineStr">
+        <is>
+          <t>25%</t>
         </is>
       </c>
       <c r="M55" s="27" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="L56" s="53" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M56" s="27" t="inlineStr">
@@ -4451,9 +4451,9 @@
           <t>0/13</t>
         </is>
       </c>
-      <c r="L57" s="65" t="inlineStr">
-        <is>
-          <t>70%</t>
+      <c r="L57" s="53" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="M57" s="27" t="inlineStr">
@@ -4569,9 +4569,9 @@
           <t>0/9</t>
         </is>
       </c>
-      <c r="L59" s="65" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="L59" s="53" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="M59" s="27" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L60" s="53" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M60" s="27" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="L65" s="53" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M65" s="27" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="L68" s="53" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M68" s="27" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="L69" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M69" s="27" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="L73" s="53" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="M73" s="27" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L76" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="M76" s="27" t="inlineStr">
@@ -5867,9 +5867,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L81" s="67" t="inlineStr">
-        <is>
-          <t>94%</t>
+      <c r="L81" s="65" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
       <c r="M81" s="65" t="inlineStr">
@@ -5949,14 +5949,14 @@
         </is>
       </c>
       <c r="C83" s="23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D83" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" s="53" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F83" s="23" t="n">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="L83" s="53" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="M83" s="27" t="inlineStr">
@@ -6044,9 +6044,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L84" s="53" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="L84" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M84" s="27" t="inlineStr">
@@ -6103,9 +6103,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L85" s="53" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="L85" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M85" s="27" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="L86" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="M86" s="27" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="L87" s="53" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="M87" s="27" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="L88" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="M88" s="27" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="L89" s="53" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="M89" s="27" t="inlineStr">
@@ -6398,9 +6398,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L90" s="53" t="inlineStr">
-        <is>
-          <t>47%</t>
+      <c r="L90" s="65" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="M90" s="27" t="inlineStr">
@@ -6457,9 +6457,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L91" s="53" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="L91" s="65" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="M91" s="27" t="inlineStr">
@@ -6480,25 +6480,25 @@
         </is>
       </c>
       <c r="C92" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
       <c r="E92" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="F92" s="23" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G92" s="23" t="n">
         <v>59</v>
       </c>
       <c r="H92" s="53" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I92" s="23" t="inlineStr">
@@ -6516,9 +6516,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L92" s="53" t="inlineStr">
-        <is>
-          <t>42%</t>
+      <c r="L92" s="65" t="inlineStr">
+        <is>
+          <t>54%</t>
         </is>
       </c>
       <c r="M92" s="27" t="inlineStr">
@@ -6539,25 +6539,25 @@
         </is>
       </c>
       <c r="C93" s="23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
       <c r="E93" s="53" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="F93" s="23" t="n">
         <v>146</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H93" s="53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="I93" s="23" t="inlineStr">
@@ -6575,9 +6575,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L93" s="53" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="L93" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M93" s="27" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="L94" s="53" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M94" s="27" t="inlineStr">
@@ -6693,9 +6693,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L95" s="53" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="L95" s="65" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="M95" s="27" t="inlineStr">
@@ -6730,11 +6730,11 @@
         <v>286</v>
       </c>
       <c r="G96" s="23" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H96" s="65" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="I96" s="23" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="L96" s="65" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="M96" s="27" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="L97" s="53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="M97" s="27" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="L98" s="65" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="M98" s="27" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="L99" s="53" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="M99" s="27" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="L100" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M100" s="27" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="L101" s="65" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="M101" s="27" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L102" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="M102" s="27" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="L103" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="M103" s="27" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="L104" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="M104" s="27" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="L105" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="M105" s="27" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L106" s="53" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="M106" s="27" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="L107" s="53" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="M107" s="27" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="L108" s="53" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="M108" s="27" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="L109" s="53" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="M109" s="27" t="inlineStr">
@@ -7578,9 +7578,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L110" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L110" s="65" t="inlineStr">
+        <is>
+          <t>52%</t>
         </is>
       </c>
       <c r="M110" s="27" t="inlineStr">
@@ -7615,11 +7615,11 @@
         <v>47</v>
       </c>
       <c r="G111" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H111" s="53" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="I111" s="23" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="L111" s="53" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="M111" s="27" t="inlineStr">
@@ -7674,11 +7674,11 @@
         <v>26</v>
       </c>
       <c r="G112" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H112" s="53" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="I112" s="23" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="L112" s="53" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="M112" s="27" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="L114" s="65" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="M114" s="27" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="L115" s="65" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="M115" s="27" t="inlineStr">
@@ -7899,11 +7899,11 @@
         <v>86</v>
       </c>
       <c r="D116" s="23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E116" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="F116" s="23" t="n">
@@ -7932,9 +7932,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L116" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+      <c r="L116" s="67" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="M116" s="65" t="inlineStr">
@@ -7969,11 +7969,11 @@
         <v>64</v>
       </c>
       <c r="G117" s="23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H117" s="65" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="I117" s="23" t="inlineStr">
@@ -7991,9 +7991,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L117" s="65" t="inlineStr">
-        <is>
-          <t>78%</t>
+      <c r="L117" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M117" s="67" t="inlineStr">
@@ -8017,11 +8017,11 @@
         <v>10</v>
       </c>
       <c r="D118" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="53" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F118" s="23" t="n">
@@ -8050,9 +8050,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L118" s="53" t="inlineStr">
-        <is>
-          <t>49%</t>
+      <c r="L118" s="65" t="inlineStr">
+        <is>
+          <t>71%</t>
         </is>
       </c>
       <c r="M118" s="65" t="inlineStr">
@@ -8109,9 +8109,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L119" s="65" t="inlineStr">
-        <is>
-          <t>77%</t>
+      <c r="L119" s="67" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="M119" s="65" t="inlineStr">
@@ -8168,9 +8168,9 @@
           <t>4/8</t>
         </is>
       </c>
-      <c r="L120" s="65" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="L120" s="67" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="M120" s="65" t="inlineStr">
@@ -8227,9 +8227,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L121" s="53" t="inlineStr">
-        <is>
-          <t>48%</t>
+      <c r="L121" s="65" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="M121" s="27" t="inlineStr">
@@ -8264,21 +8264,21 @@
         <v>214</v>
       </c>
       <c r="G122" s="23" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="H122" s="65" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I122" s="23" t="inlineStr">
         <is>
-          <t>72/89</t>
+          <t>74/89</t>
         </is>
       </c>
       <c r="J122" s="23" t="inlineStr">
         <is>
-          <t>26/50</t>
+          <t>33/50</t>
         </is>
       </c>
       <c r="K122" s="23" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="L122" s="65" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="M122" s="27" t="inlineStr">
@@ -8323,11 +8323,11 @@
         <v>73</v>
       </c>
       <c r="G123" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H123" s="53" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="I123" s="23" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="J123" s="23" t="inlineStr">
         <is>
-          <t>16/38</t>
+          <t>17/38</t>
         </is>
       </c>
       <c r="K123" s="23" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="L123" s="53" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="M123" s="27" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="L124" s="53" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M124" s="27" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="L125" s="65" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M125" s="27" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="L126" s="53" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="M126" s="27" t="inlineStr">
@@ -8581,9 +8581,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L127" s="53" t="inlineStr">
-        <is>
-          <t>48%</t>
+      <c r="L127" s="65" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="M127" s="65" t="inlineStr">
@@ -8640,9 +8640,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L128" s="53" t="inlineStr">
-        <is>
-          <t>42%</t>
+      <c r="L128" s="65" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="M128" s="27" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="L129" s="53" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="M129" s="27" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="L130" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="M130" s="27" t="inlineStr">
@@ -8817,9 +8817,9 @@
           <t>6/12</t>
         </is>
       </c>
-      <c r="L131" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L131" s="65" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="M131" s="27" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="L132" s="53" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="M132" s="27" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="L133" s="53" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="M133" s="27" t="inlineStr">
@@ -8972,7 +8972,7 @@
         <v>215</v>
       </c>
       <c r="G134" s="23" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H134" s="53" t="inlineStr">
         <is>
@@ -8994,9 +8994,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L134" s="53" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="L134" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M134" s="27" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="L135" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M135" s="27" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="L136" s="53" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="M136" s="27" t="inlineStr">
@@ -9171,9 +9171,9 @@
           <t>6/12</t>
         </is>
       </c>
-      <c r="L137" s="53" t="inlineStr">
-        <is>
-          <t>43%</t>
+      <c r="L137" s="65" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="M137" s="27" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="L138" s="65" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="M138" s="27" t="inlineStr">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="C139" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D139" s="23" t="n">
         <v>0</v>
@@ -9267,11 +9267,11 @@
         <v>73</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H139" s="65" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="I139" s="23" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="L139" s="65" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="M139" s="27" t="inlineStr">
@@ -9312,25 +9312,25 @@
         </is>
       </c>
       <c r="C140" s="23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D140" s="23" t="n">
         <v>1</v>
       </c>
       <c r="E140" s="53" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="F140" s="23" t="n">
         <v>68</v>
       </c>
       <c r="G140" s="23" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H140" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I140" s="23" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="L140" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="M140" s="27" t="inlineStr">
@@ -9385,11 +9385,11 @@
         <v>43</v>
       </c>
       <c r="G141" s="23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H141" s="65" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="I141" s="23" t="inlineStr">
@@ -9407,9 +9407,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L141" s="65" t="inlineStr">
-        <is>
-          <t>65%</t>
+      <c r="L141" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M141" s="67" t="inlineStr">
@@ -9444,11 +9444,11 @@
         <v>42</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H142" s="65" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I142" s="23" t="inlineStr">
@@ -9466,9 +9466,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L142" s="65" t="inlineStr">
-        <is>
-          <t>60%</t>
+      <c r="L142" s="67" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="M142" s="65" t="inlineStr">
@@ -9503,11 +9503,11 @@
         <v>17</v>
       </c>
       <c r="G143" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H143" s="65" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I143" s="23" t="inlineStr">
@@ -9525,9 +9525,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L143" s="65" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="L143" s="67" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="M143" s="65" t="inlineStr">
@@ -9584,9 +9584,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L144" s="65" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="L144" s="67" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="M144" s="65" t="inlineStr">
@@ -9643,9 +9643,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L145" s="65" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="L145" s="67" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="M145" s="27" t="inlineStr">
@@ -9702,9 +9702,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L146" s="65" t="inlineStr">
-        <is>
-          <t>71%</t>
+      <c r="L146" s="67" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
       <c r="M146" s="27" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="L147" s="53" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M147" s="27" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="L148" s="53" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M148" s="27" t="inlineStr">
@@ -9857,11 +9857,11 @@
         <v>17</v>
       </c>
       <c r="G149" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H149" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="I149" s="23" t="inlineStr">
@@ -9879,9 +9879,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L149" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L149" s="65" t="inlineStr">
+        <is>
+          <t>54%</t>
         </is>
       </c>
       <c r="M149" s="27" t="inlineStr">
@@ -9916,11 +9916,11 @@
         <v>47</v>
       </c>
       <c r="G150" s="23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H150" s="65" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="I150" s="23" t="inlineStr">
@@ -9938,9 +9938,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L150" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+      <c r="L150" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M150" s="67" t="inlineStr">
@@ -9975,11 +9975,11 @@
         <v>42</v>
       </c>
       <c r="G151" s="23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H151" s="65" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="I151" s="23" t="inlineStr">
@@ -9997,9 +9997,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L151" s="65" t="inlineStr">
-        <is>
-          <t>81%</t>
+      <c r="L151" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M151" s="67" t="inlineStr">
@@ -10034,11 +10034,11 @@
         <v>43</v>
       </c>
       <c r="G152" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H152" s="65" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="I152" s="23" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L152" s="65" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="M152" s="27" t="inlineStr">
@@ -10093,11 +10093,11 @@
         <v>43</v>
       </c>
       <c r="G153" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H153" s="65" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="I153" s="23" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="L153" s="65" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="M153" s="27" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="L154" s="65" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="M154" s="27" t="inlineStr">
@@ -10233,9 +10233,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L155" s="53" t="inlineStr">
-        <is>
-          <t>49%</t>
+      <c r="L155" s="65" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="M155" s="27" t="inlineStr">
@@ -10270,11 +10270,11 @@
         <v>43</v>
       </c>
       <c r="G156" s="23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H156" s="53" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="I156" s="23" t="inlineStr">
@@ -10292,9 +10292,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L156" s="53" t="inlineStr">
-        <is>
-          <t>44%</t>
+      <c r="L156" s="65" t="inlineStr">
+        <is>
+          <t>56%</t>
         </is>
       </c>
       <c r="M156" s="27" t="inlineStr">
@@ -10329,11 +10329,11 @@
         <v>35</v>
       </c>
       <c r="G157" s="23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H157" s="65" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="I157" s="23" t="inlineStr">
@@ -10351,9 +10351,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L157" s="65" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="L157" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M157" s="67" t="inlineStr">
@@ -10388,11 +10388,11 @@
         <v>34</v>
       </c>
       <c r="G158" s="23" t="n">
-        <v>29</v>
-      </c>
-      <c r="H158" s="65" t="inlineStr">
-        <is>
-          <t>85%</t>
+        <v>31</v>
+      </c>
+      <c r="H158" s="67" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="I158" s="23" t="inlineStr">
@@ -10410,9 +10410,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L158" s="65" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="L158" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M158" s="67" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="L159" s="65" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="M159" s="27" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="L160" s="65" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="M160" s="27" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="L161" s="65" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="M161" s="27" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="L162" s="65" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="M162" s="27" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="L163" s="65" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M163" s="27" t="inlineStr">
@@ -10742,11 +10742,11 @@
         <v>44</v>
       </c>
       <c r="G164" s="23" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H164" s="65" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="I164" s="23" t="inlineStr">
@@ -10764,9 +10764,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L164" s="65" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="L164" s="67" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="M164" s="65" t="inlineStr">
@@ -10823,9 +10823,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L165" s="65" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="L165" s="67" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="M165" s="65" t="inlineStr">
@@ -10846,25 +10846,25 @@
         </is>
       </c>
       <c r="C166" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
       <c r="E166" s="65" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="F166" s="23" t="n">
         <v>44</v>
       </c>
       <c r="G166" s="23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H166" s="65" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="I166" s="23" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="J166" s="23" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>10/11</t>
         </is>
       </c>
       <c r="K166" s="23" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="L166" s="65" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="M166" s="27" t="inlineStr">
@@ -10905,25 +10905,25 @@
         </is>
       </c>
       <c r="C167" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
       <c r="E167" s="53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F167" s="23" t="n">
         <v>44</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H167" s="65" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="I167" s="23" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="L167" s="65" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="M167" s="27" t="inlineStr">
@@ -11000,9 +11000,9 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L168" s="53" t="inlineStr">
-        <is>
-          <t>48%</t>
+      <c r="L168" s="65" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="M168" s="27" t="inlineStr">
@@ -11059,9 +11059,9 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L169" s="53" t="inlineStr">
-        <is>
-          <t>48%</t>
+      <c r="L169" s="65" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="M169" s="27" t="inlineStr">
@@ -11096,11 +11096,11 @@
         <v>44</v>
       </c>
       <c r="G170" s="23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H170" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I170" s="23" t="inlineStr">
@@ -11118,9 +11118,9 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L170" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L170" s="65" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="M170" s="27" t="inlineStr">
@@ -11177,9 +11177,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L171" s="65" t="inlineStr">
-        <is>
-          <t>82%</t>
+      <c r="L171" s="67" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="M171" s="65" t="inlineStr">
@@ -11214,11 +11214,11 @@
         <v>41</v>
       </c>
       <c r="G172" s="23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H172" s="65" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I172" s="23" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="L172" s="65" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="M172" s="65" t="inlineStr">
@@ -11295,9 +11295,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L173" s="65" t="inlineStr">
-        <is>
-          <t>86%</t>
+      <c r="L173" s="67" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="M173" s="65" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="L174" s="65" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="M174" s="65" t="inlineStr">
@@ -11391,21 +11391,21 @@
         <v>73</v>
       </c>
       <c r="G175" s="23" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H175" s="65" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I175" s="23" t="inlineStr">
         <is>
-          <t>16/38</t>
+          <t>24/38</t>
         </is>
       </c>
       <c r="J175" s="23" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="K175" s="23" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="L175" s="65" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="M175" s="27" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="L176" s="65" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="M176" s="27" t="inlineStr">
@@ -11509,16 +11509,16 @@
         <v>73</v>
       </c>
       <c r="G177" s="23" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H177" s="65" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="I177" s="23" t="inlineStr">
         <is>
-          <t>17/38</t>
+          <t>23/38</t>
         </is>
       </c>
       <c r="J177" s="23" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L177" s="65" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="M177" s="27" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="L178" s="53" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="M178" s="27" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="L179" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="M179" s="27" t="inlineStr">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="L180" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="M180" s="27" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="L181" s="53" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="M181" s="27" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="L182" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="M182" s="27" t="inlineStr">
@@ -11863,11 +11863,11 @@
         <v>73</v>
       </c>
       <c r="G183" s="23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H183" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="I183" s="23" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="L183" s="53" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M183" s="27" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="L184" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="M184" s="27" t="inlineStr">
@@ -12003,9 +12003,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L185" s="65" t="inlineStr">
-        <is>
-          <t>77%</t>
+      <c r="L185" s="67" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="M185" s="65" t="inlineStr">
@@ -12062,9 +12062,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L186" s="65" t="inlineStr">
-        <is>
-          <t>88%</t>
+      <c r="L186" s="67" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="M186" s="65" t="inlineStr">
@@ -12099,11 +12099,11 @@
         <v>78</v>
       </c>
       <c r="G187" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H187" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I187" s="23" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="L187" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="M187" s="27" t="inlineStr">
@@ -12158,11 +12158,11 @@
         <v>78</v>
       </c>
       <c r="G188" s="23" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H188" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="I188" s="23" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="L188" s="65" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="M188" s="27" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="L189" s="65" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="M189" s="27" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="L190" s="65" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="M190" s="27" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="L191" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="M191" s="27" t="inlineStr">
@@ -12394,16 +12394,16 @@
         <v>399</v>
       </c>
       <c r="G192" s="23" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="H192" s="65" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="I192" s="23" t="inlineStr">
         <is>
-          <t>47/74</t>
+          <t>51/74</t>
         </is>
       </c>
       <c r="J192" s="23" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="L192" s="65" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="M192" s="27" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="L193" s="53" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="M193" s="27" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="L194" s="53" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="M194" s="27" t="inlineStr">
@@ -12652,9 +12652,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L196" s="65" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="L196" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M196" s="67" t="inlineStr">
@@ -12689,16 +12689,16 @@
         <v>130</v>
       </c>
       <c r="G197" s="23" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H197" s="53" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I197" s="23" t="inlineStr">
         <is>
-          <t>48/94</t>
+          <t>52/94</t>
         </is>
       </c>
       <c r="J197" s="23" t="inlineStr">
@@ -12711,9 +12711,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L197" s="53" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="L197" s="65" t="inlineStr">
+        <is>
+          <t>55%</t>
         </is>
       </c>
       <c r="M197" s="27" t="inlineStr">
@@ -12770,9 +12770,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L198" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+      <c r="L198" s="67" t="inlineStr">
+        <is>
+          <t>99%</t>
         </is>
       </c>
       <c r="M198" s="27" t="inlineStr">
@@ -12829,9 +12829,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L199" s="65" t="inlineStr">
-        <is>
-          <t>66%</t>
+      <c r="L199" s="53" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="M199" s="27" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="L200" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M200" s="27" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="L201" s="53" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M201" s="27" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="L202" s="53" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M202" s="27" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="L206" s="53" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="M206" s="27" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="L207" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M207" s="27" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="L208" s="53" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M208" s="27" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="L209" s="53" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M209" s="27" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="L211" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M211" s="27" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="L212" s="53" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="M212" s="27" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="L213" s="53" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M213" s="27" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="L214" s="53" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="M214" s="27" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="L215" s="53" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="M215" s="27" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="L216" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M216" s="27" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L226" s="53" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="M226" s="27" t="inlineStr">
@@ -14540,9 +14540,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L228" s="53" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="L228" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M228" s="65" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="L233" s="53" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="M233" s="27" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="L234" s="53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="M234" s="27" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="L236" s="53" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="M236" s="27" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="L237" s="53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M237" s="27" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="L238" s="53" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="M238" s="27" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="L239" s="53" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="M239" s="27" t="inlineStr">
@@ -15226,16 +15226,16 @@
         <v>88</v>
       </c>
       <c r="G240" s="23" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H240" s="65" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="I240" s="23" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>20/25</t>
         </is>
       </c>
       <c r="J240" s="23" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="L240" s="65" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="M240" s="27" t="inlineStr">
@@ -15307,9 +15307,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L241" s="65" t="inlineStr">
-        <is>
-          <t>58%</t>
+      <c r="L241" s="67" t="inlineStr">
+        <is>
+          <t>95%</t>
         </is>
       </c>
       <c r="M241" s="65" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="L242" s="53" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="M242" s="27" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="L243" s="53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M243" s="27" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="L244" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="M244" s="27" t="inlineStr">
@@ -15543,9 +15543,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L245" s="53" t="inlineStr">
-        <is>
-          <t>40%</t>
+      <c r="L245" s="65" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="M245" s="27" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="L246" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="M246" s="27" t="inlineStr">
@@ -15661,9 +15661,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L247" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+      <c r="L247" s="65" t="inlineStr">
+        <is>
+          <t>52%</t>
         </is>
       </c>
       <c r="M247" s="27" t="inlineStr">
@@ -15720,9 +15720,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L248" s="53" t="inlineStr">
-        <is>
-          <t>46%</t>
+      <c r="L248" s="65" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="M248" s="27" t="inlineStr">
@@ -15757,11 +15757,11 @@
         <v>52</v>
       </c>
       <c r="G249" s="23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H249" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="I249" s="23" t="inlineStr">
@@ -15781,7 +15781,7 @@
       </c>
       <c r="L249" s="53" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="M249" s="27" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="L250" s="65" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="M250" s="27" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="L251" s="65" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="M251" s="27" t="inlineStr">
@@ -15956,9 +15956,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L252" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+      <c r="L252" s="67" t="inlineStr">
+        <is>
+          <t>98%</t>
         </is>
       </c>
       <c r="M252" s="27" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="L253" s="65" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="M253" s="27" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="L254" s="53" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="M254" s="27" t="inlineStr">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="L255" s="53" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="M255" s="27" t="inlineStr">
@@ -16192,9 +16192,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L256" s="53" t="inlineStr">
-        <is>
-          <t>37%</t>
+      <c r="L256" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M256" s="27" t="inlineStr">
@@ -16229,11 +16229,11 @@
         <v>22</v>
       </c>
       <c r="G257" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H257" s="53" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="I257" s="23" t="inlineStr">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="L257" s="53" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="M257" s="27" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="L258" s="53" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="M258" s="27" t="inlineStr">
@@ -16347,11 +16347,11 @@
         <v>55</v>
       </c>
       <c r="G259" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H259" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="I259" s="23" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="L259" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="M259" s="27" t="inlineStr">
@@ -16406,11 +16406,11 @@
         <v>54</v>
       </c>
       <c r="G260" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H260" s="53" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="I260" s="23" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="L260" s="53" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="M260" s="27" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="L261" s="65" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="M261" s="65" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="L262" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M262" s="27" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="L263" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M263" s="27" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="L264" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M264" s="27" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="L265" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="M265" s="27" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="L266" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M266" s="27" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="L267" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M267" s="27" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="L268" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M268" s="27" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="L269" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M269" s="27" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="L270" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M270" s="27" t="inlineStr">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="L271" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M271" s="27" t="inlineStr">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="L272" s="53" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="M272" s="27" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="L274" s="65" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="M274" s="27" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="L275" s="53" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="M275" s="27" t="inlineStr">
@@ -17431,9 +17431,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L277" s="53" t="inlineStr">
-        <is>
-          <t>36%</t>
+      <c r="L277" s="65" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="M277" s="27" t="inlineStr">
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L281" s="65" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="M281" s="27" t="inlineStr">
@@ -17926,25 +17926,25 @@
         </is>
       </c>
       <c r="C286" s="23" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
       <c r="E286" s="53" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="F286" s="23" t="n">
         <v>194</v>
       </c>
       <c r="G286" s="23" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H286" s="65" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="I286" s="23" t="inlineStr">
@@ -17962,9 +17962,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L286" s="65" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="L286" s="67" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M286" s="67" t="inlineStr">

--- a/EXCEL/6 - SUBSYSTEM.xlsx
+++ b/EXCEL/6 - SUBSYSTEM.xlsx
@@ -67,7 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFc00000"/>
+      <color rgb="FFed7d31"/>
       <sz val="10"/>
     </font>
     <font>
@@ -79,7 +79,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
+      <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -674,9 +674,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -686,10 +683,13 @@
     <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -701,7 +701,7 @@
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1234,7 +1234,7 @@
       <c r="D3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -1245,7 +1245,7 @@
       <c r="G3" s="23" t="n">
         <v>44</v>
       </c>
-      <c r="H3" s="53" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L3" s="53" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="M3" s="27" t="inlineStr">
@@ -1293,7 +1293,7 @@
       <c r="D4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="53" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -1304,7 +1304,7 @@
       <c r="G4" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="53" t="inlineStr">
+      <c r="H4" s="68" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -1324,7 +1324,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L4" s="65" t="inlineStr">
+      <c r="L4" s="53" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -1352,7 +1352,7 @@
       <c r="D5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1363,7 +1363,7 @@
       <c r="G5" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="68" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -1383,9 +1383,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L5" s="65" t="inlineStr">
-        <is>
-          <t>58%</t>
+      <c r="L5" s="53" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="M5" s="27" t="inlineStr">
@@ -1422,7 +1422,7 @@
       <c r="G6" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="53" t="inlineStr">
+      <c r="H6" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1442,7 +1442,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L6" s="65" t="inlineStr">
+      <c r="L6" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -1470,7 +1470,7 @@
       <c r="D7" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="53" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -1481,7 +1481,7 @@
       <c r="G7" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -1501,7 +1501,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L7" s="65" t="inlineStr">
+      <c r="L7" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -1529,7 +1529,7 @@
       <c r="D8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1540,7 +1540,7 @@
       <c r="G8" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="65" t="inlineStr">
+      <c r="H8" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -1560,7 +1560,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L8" s="65" t="inlineStr">
+      <c r="L8" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -1599,7 +1599,7 @@
       <c r="G9" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1619,9 +1619,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L9" s="65" t="inlineStr">
-        <is>
-          <t>51%</t>
+      <c r="L9" s="53" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="M9" s="27" t="inlineStr">
@@ -1647,7 +1647,7 @@
       <c r="D10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="53" t="inlineStr">
+      <c r="E10" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -1658,7 +1658,7 @@
       <c r="G10" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -1678,9 +1678,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L10" s="65" t="inlineStr">
-        <is>
-          <t>52%</t>
+      <c r="L10" s="53" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="M10" s="27" t="inlineStr">
@@ -1706,7 +1706,7 @@
       <c r="D11" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>83%</t>
         </is>
@@ -1717,7 +1717,7 @@
       <c r="G11" s="23" t="n">
         <v>217</v>
       </c>
-      <c r="H11" s="67" t="inlineStr">
+      <c r="H11" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1737,7 +1737,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L11" s="67" t="inlineStr">
+      <c r="L11" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1765,7 +1765,7 @@
       <c r="D12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="53" t="inlineStr">
+      <c r="E12" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -1774,11 +1774,11 @@
         <v>151</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>52</v>
-      </c>
-      <c r="H12" s="53" t="inlineStr">
-        <is>
-          <t>34%</t>
+        <v>67</v>
+      </c>
+      <c r="H12" s="68" t="inlineStr">
+        <is>
+          <t>44%</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>5/44</t>
+          <t>20/44</t>
         </is>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -1796,7 +1796,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L12" s="53" t="inlineStr">
+      <c r="L12" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -1824,7 +1824,7 @@
       <c r="D13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1833,11 +1833,11 @@
         <v>116</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="53" t="inlineStr">
-        <is>
-          <t>4%</t>
+        <v>8</v>
+      </c>
+      <c r="H13" s="68" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>0/74</t>
+          <t>3/74</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr">
@@ -1855,9 +1855,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L13" s="53" t="inlineStr">
-        <is>
-          <t>4%</t>
+      <c r="L13" s="68" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="M13" s="27" t="inlineStr">
@@ -1883,7 +1883,7 @@
       <c r="D14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="53" t="inlineStr">
+      <c r="E14" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1894,7 +1894,7 @@
       <c r="G14" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="53" t="inlineStr">
+      <c r="H14" s="68" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -1914,7 +1914,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L14" s="53" t="inlineStr">
+      <c r="L14" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -1942,7 +1942,7 @@
       <c r="D15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="53" t="inlineStr">
+      <c r="E15" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1953,7 +1953,7 @@
       <c r="G15" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="53" t="inlineStr">
+      <c r="H15" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -1973,7 +1973,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L15" s="53" t="inlineStr">
+      <c r="L15" s="68" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -2012,7 +2012,7 @@
       <c r="G16" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H16" s="53" t="inlineStr">
+      <c r="H16" s="68" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -2032,7 +2032,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L16" s="53" t="inlineStr">
+      <c r="L16" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -2071,7 +2071,7 @@
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="53" t="inlineStr">
+      <c r="H17" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -2091,7 +2091,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L17" s="53" t="inlineStr">
+      <c r="L17" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2130,7 +2130,7 @@
       <c r="G18" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="H18" s="53" t="inlineStr">
+      <c r="H18" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2150,7 +2150,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L18" s="53" t="inlineStr">
+      <c r="L18" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -2178,7 +2178,7 @@
       <c r="D19" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2187,11 +2187,11 @@
         <v>86</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H19" s="53" t="inlineStr">
-        <is>
-          <t>17%</t>
+        <v>30</v>
+      </c>
+      <c r="H19" s="68" t="inlineStr">
+        <is>
+          <t>35%</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>15/62</t>
+          <t>30/62</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr">
@@ -2209,9 +2209,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L19" s="53" t="inlineStr">
-        <is>
-          <t>24%</t>
+      <c r="L19" s="68" t="inlineStr">
+        <is>
+          <t>48%</t>
         </is>
       </c>
       <c r="M19" s="27" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="G20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="53" t="inlineStr">
+      <c r="H20" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -2268,7 +2268,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L20" s="53" t="inlineStr">
+      <c r="L20" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -2307,7 +2307,7 @@
       <c r="G21" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="53" t="inlineStr">
+      <c r="H21" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -2327,7 +2327,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L21" s="53" t="inlineStr">
+      <c r="L21" s="68" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -2355,7 +2355,7 @@
       <c r="D22" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="53" t="inlineStr">
+      <c r="E22" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2366,7 +2366,7 @@
       <c r="G22" s="23" t="n">
         <v>42</v>
       </c>
-      <c r="H22" s="65" t="inlineStr">
+      <c r="H22" s="53" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
@@ -2386,9 +2386,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L22" s="65" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="L22" s="53" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="M22" s="27" t="inlineStr">
@@ -2425,7 +2425,7 @@
       <c r="G23" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H23" s="53" t="inlineStr">
+      <c r="H23" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -2445,7 +2445,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L23" s="53" t="inlineStr">
+      <c r="L23" s="68" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -2484,7 +2484,7 @@
       <c r="G24" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="53" t="inlineStr">
+      <c r="H24" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -2504,7 +2504,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L24" s="53" t="inlineStr">
+      <c r="L24" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -2543,7 +2543,7 @@
       <c r="G25" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="53" t="inlineStr">
+      <c r="H25" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -2563,7 +2563,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L25" s="53" t="inlineStr">
+      <c r="L25" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -2602,7 +2602,7 @@
       <c r="G26" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="53" t="inlineStr">
+      <c r="H26" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2622,7 +2622,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L26" s="53" t="inlineStr">
+      <c r="L26" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2650,7 +2650,7 @@
       <c r="D27" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="53" t="inlineStr">
+      <c r="E27" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2661,7 +2661,7 @@
       <c r="G27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="H27" s="53" t="inlineStr">
+      <c r="H27" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -2681,7 +2681,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L27" s="53" t="inlineStr">
+      <c r="L27" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2720,7 +2720,7 @@
       <c r="G28" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="53" t="inlineStr">
+      <c r="H28" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2740,7 +2740,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L28" s="53" t="inlineStr">
+      <c r="L28" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2779,7 +2779,7 @@
       <c r="G29" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="53" t="inlineStr">
+      <c r="H29" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2799,7 +2799,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L29" s="53" t="inlineStr">
+      <c r="L29" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2838,7 +2838,7 @@
       <c r="G30" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="53" t="inlineStr">
+      <c r="H30" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2858,7 +2858,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L30" s="53" t="inlineStr">
+      <c r="L30" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2897,7 +2897,7 @@
       <c r="G31" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="53" t="inlineStr">
+      <c r="H31" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2917,7 +2917,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L31" s="53" t="inlineStr">
+      <c r="L31" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2956,7 +2956,7 @@
       <c r="G32" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="53" t="inlineStr">
+      <c r="H32" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -2976,7 +2976,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L32" s="53" t="inlineStr">
+      <c r="L32" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3004,7 +3004,7 @@
       <c r="D33" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="53" t="inlineStr">
+      <c r="E33" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3015,7 +3015,7 @@
       <c r="G33" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H33" s="65" t="inlineStr">
+      <c r="H33" s="53" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -3035,7 +3035,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L33" s="67" t="inlineStr">
+      <c r="L33" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3074,7 +3074,7 @@
       <c r="G34" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="53" t="inlineStr">
+      <c r="H34" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3094,7 +3094,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L34" s="53" t="inlineStr">
+      <c r="L34" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3133,7 +3133,7 @@
       <c r="G35" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="53" t="inlineStr">
+      <c r="H35" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3153,7 +3153,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L35" s="53" t="inlineStr">
+      <c r="L35" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3181,7 +3181,7 @@
       <c r="D36" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="53" t="inlineStr">
+      <c r="E36" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3192,7 +3192,7 @@
       <c r="G36" s="23" t="n">
         <v>95</v>
       </c>
-      <c r="H36" s="67" t="inlineStr">
+      <c r="H36" s="66" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3212,7 +3212,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L36" s="67" t="inlineStr">
+      <c r="L36" s="66" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -3251,7 +3251,7 @@
       <c r="G37" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="53" t="inlineStr">
+      <c r="H37" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3271,7 +3271,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L37" s="53" t="inlineStr">
+      <c r="L37" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3310,7 +3310,7 @@
       <c r="G38" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="53" t="inlineStr">
+      <c r="H38" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3330,7 +3330,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L38" s="53" t="inlineStr">
+      <c r="L38" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3369,7 +3369,7 @@
       <c r="G39" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="53" t="inlineStr">
+      <c r="H39" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3389,7 +3389,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L39" s="53" t="inlineStr">
+      <c r="L39" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3428,7 +3428,7 @@
       <c r="G40" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="53" t="inlineStr">
+      <c r="H40" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3448,7 +3448,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L40" s="53" t="inlineStr">
+      <c r="L40" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3476,7 +3476,7 @@
       <c r="D41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="65" t="inlineStr">
+      <c r="E41" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -3487,7 +3487,7 @@
       <c r="G41" s="23" t="n">
         <v>77</v>
       </c>
-      <c r="H41" s="67" t="inlineStr">
+      <c r="H41" s="66" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3507,7 +3507,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L41" s="67" t="inlineStr">
+      <c r="L41" s="66" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3535,7 +3535,7 @@
       <c r="D42" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="E42" s="65" t="inlineStr">
+      <c r="E42" s="53" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -3546,7 +3546,7 @@
       <c r="G42" s="23" t="n">
         <v>382</v>
       </c>
-      <c r="H42" s="67" t="inlineStr">
+      <c r="H42" s="66" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3566,7 +3566,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L42" s="67" t="inlineStr">
+      <c r="L42" s="66" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -3594,7 +3594,7 @@
       <c r="D43" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E43" s="67" t="inlineStr">
+      <c r="E43" s="66" t="inlineStr">
         <is>
           <t>93%</t>
         </is>
@@ -3605,7 +3605,7 @@
       <c r="G43" s="23" t="n">
         <v>416</v>
       </c>
-      <c r="H43" s="65" t="inlineStr">
+      <c r="H43" s="53" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3625,7 +3625,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L43" s="65" t="inlineStr">
+      <c r="L43" s="53" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3653,7 +3653,7 @@
       <c r="D44" s="23" t="n">
         <v>69</v>
       </c>
-      <c r="E44" s="67" t="inlineStr">
+      <c r="E44" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -3664,7 +3664,7 @@
       <c r="G44" s="23" t="n">
         <v>113</v>
       </c>
-      <c r="H44" s="65" t="inlineStr">
+      <c r="H44" s="53" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -3684,12 +3684,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L44" s="67" t="inlineStr">
+      <c r="L44" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M44" s="65" t="inlineStr">
+      <c r="M44" s="53" t="inlineStr">
         <is>
           <t>PARTIAL(22-08-2026)</t>
         </is>
@@ -3712,7 +3712,7 @@
       <c r="D45" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="53" t="inlineStr">
+      <c r="E45" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3723,7 +3723,7 @@
       <c r="G45" s="23" t="n">
         <v>62</v>
       </c>
-      <c r="H45" s="65" t="inlineStr">
+      <c r="H45" s="53" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -3743,12 +3743,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L45" s="67" t="inlineStr">
+      <c r="L45" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M45" s="67" t="inlineStr">
+      <c r="M45" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -3771,7 +3771,7 @@
       <c r="D46" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E46" s="65" t="inlineStr">
+      <c r="E46" s="53" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -3782,7 +3782,7 @@
       <c r="G46" s="23" t="n">
         <v>129</v>
       </c>
-      <c r="H46" s="65" t="inlineStr">
+      <c r="H46" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -3802,7 +3802,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L46" s="65" t="inlineStr">
+      <c r="L46" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -3830,7 +3830,7 @@
       <c r="D47" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E47" s="65" t="inlineStr">
+      <c r="E47" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -3841,7 +3841,7 @@
       <c r="G47" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H47" s="65" t="inlineStr">
+      <c r="H47" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -3861,12 +3861,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L47" s="67" t="inlineStr">
+      <c r="L47" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M47" s="67" t="inlineStr">
+      <c r="M47" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -3900,7 +3900,7 @@
       <c r="G48" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="53" t="inlineStr">
+      <c r="H48" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3920,7 +3920,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L48" s="53" t="inlineStr">
+      <c r="L48" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3959,7 +3959,7 @@
       <c r="G49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="53" t="inlineStr">
+      <c r="H49" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -3979,7 +3979,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L49" s="53" t="inlineStr">
+      <c r="L49" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4018,7 +4018,7 @@
       <c r="G50" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="53" t="inlineStr">
+      <c r="H50" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4038,7 +4038,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L50" s="53" t="inlineStr">
+      <c r="L50" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4066,7 +4066,7 @@
       <c r="D51" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="53" t="inlineStr">
+      <c r="E51" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4077,7 +4077,7 @@
       <c r="G51" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="H51" s="53" t="inlineStr">
+      <c r="H51" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -4097,7 +4097,7 @@
           <t>12/230</t>
         </is>
       </c>
-      <c r="L51" s="53" t="inlineStr">
+      <c r="L51" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -4136,7 +4136,7 @@
       <c r="G52" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="53" t="inlineStr">
+      <c r="H52" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -4156,7 +4156,7 @@
           <t>2/18</t>
         </is>
       </c>
-      <c r="L52" s="53" t="inlineStr">
+      <c r="L52" s="68" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -4195,7 +4195,7 @@
       <c r="G53" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="53" t="inlineStr">
+      <c r="H53" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4215,7 +4215,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L53" s="53" t="inlineStr">
+      <c r="L53" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4254,7 +4254,7 @@
       <c r="G54" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="53" t="inlineStr">
+      <c r="H54" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4274,7 +4274,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L54" s="53" t="inlineStr">
+      <c r="L54" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4302,7 +4302,7 @@
       <c r="D55" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E55" s="53" t="inlineStr">
+      <c r="E55" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4313,7 +4313,7 @@
       <c r="G55" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="H55" s="65" t="inlineStr">
+      <c r="H55" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -4333,7 +4333,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L55" s="53" t="inlineStr">
+      <c r="L55" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4372,7 +4372,7 @@
       <c r="G56" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H56" s="53" t="inlineStr">
+      <c r="H56" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -4392,7 +4392,7 @@
           <t>0/34</t>
         </is>
       </c>
-      <c r="L56" s="53" t="inlineStr">
+      <c r="L56" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4420,7 +4420,7 @@
       <c r="D57" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="65" t="inlineStr">
+      <c r="E57" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -4431,7 +4431,7 @@
       <c r="G57" s="23" t="n">
         <v>69</v>
       </c>
-      <c r="H57" s="65" t="inlineStr">
+      <c r="H57" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -4451,7 +4451,7 @@
           <t>0/13</t>
         </is>
       </c>
-      <c r="L57" s="53" t="inlineStr">
+      <c r="L57" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4490,7 +4490,7 @@
       <c r="G58" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="53" t="inlineStr">
+      <c r="H58" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4510,7 +4510,7 @@
           <t>0/12</t>
         </is>
       </c>
-      <c r="L58" s="53" t="inlineStr">
+      <c r="L58" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4538,7 +4538,7 @@
       <c r="D59" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="53" t="inlineStr">
+      <c r="E59" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -4549,7 +4549,7 @@
       <c r="G59" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H59" s="65" t="inlineStr">
+      <c r="H59" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -4569,7 +4569,7 @@
           <t>0/9</t>
         </is>
       </c>
-      <c r="L59" s="53" t="inlineStr">
+      <c r="L59" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4597,7 +4597,7 @@
       <c r="D60" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="53" t="inlineStr">
+      <c r="E60" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4608,7 +4608,7 @@
       <c r="G60" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H60" s="53" t="inlineStr">
+      <c r="H60" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -4628,7 +4628,7 @@
           <t>0/11</t>
         </is>
       </c>
-      <c r="L60" s="53" t="inlineStr">
+      <c r="L60" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4667,7 +4667,7 @@
       <c r="G61" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="53" t="inlineStr">
+      <c r="H61" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4687,7 +4687,7 @@
           <t>0/4</t>
         </is>
       </c>
-      <c r="L61" s="53" t="inlineStr">
+      <c r="L61" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4715,7 +4715,7 @@
       <c r="D62" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="53" t="inlineStr">
+      <c r="E62" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4726,7 +4726,7 @@
       <c r="G62" s="23" t="n">
         <v>49</v>
       </c>
-      <c r="H62" s="65" t="inlineStr">
+      <c r="H62" s="53" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -4746,7 +4746,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L62" s="65" t="inlineStr">
+      <c r="L62" s="53" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -4785,7 +4785,7 @@
       <c r="G63" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H63" s="53" t="inlineStr">
+      <c r="H63" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4805,7 +4805,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L63" s="53" t="inlineStr">
+      <c r="L63" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4844,7 +4844,7 @@
       <c r="G64" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="53" t="inlineStr">
+      <c r="H64" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4864,7 +4864,7 @@
           <t>0/18</t>
         </is>
       </c>
-      <c r="L64" s="53" t="inlineStr">
+      <c r="L64" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4903,7 +4903,7 @@
       <c r="G65" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H65" s="53" t="inlineStr">
+      <c r="H65" s="68" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -4923,7 +4923,7 @@
           <t>0/73</t>
         </is>
       </c>
-      <c r="L65" s="53" t="inlineStr">
+      <c r="L65" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4962,7 +4962,7 @@
       <c r="G66" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="53" t="inlineStr">
+      <c r="H66" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -4982,7 +4982,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L66" s="53" t="inlineStr">
+      <c r="L66" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5021,7 +5021,7 @@
       <c r="G67" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="53" t="inlineStr">
+      <c r="H67" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5041,7 +5041,7 @@
           <t>0/10</t>
         </is>
       </c>
-      <c r="L67" s="53" t="inlineStr">
+      <c r="L67" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5080,7 +5080,7 @@
       <c r="G68" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H68" s="53" t="inlineStr">
+      <c r="H68" s="68" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -5100,7 +5100,7 @@
           <t>0/250</t>
         </is>
       </c>
-      <c r="L68" s="53" t="inlineStr">
+      <c r="L68" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5139,7 +5139,7 @@
       <c r="G69" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H69" s="53" t="inlineStr">
+      <c r="H69" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -5159,7 +5159,7 @@
           <t>0/6</t>
         </is>
       </c>
-      <c r="L69" s="53" t="inlineStr">
+      <c r="L69" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5198,7 +5198,7 @@
       <c r="G70" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H70" s="53" t="inlineStr">
+      <c r="H70" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5218,7 +5218,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L70" s="53" t="inlineStr">
+      <c r="L70" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5257,7 +5257,7 @@
       <c r="G71" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="53" t="inlineStr">
+      <c r="H71" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5277,7 +5277,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L71" s="53" t="inlineStr">
+      <c r="L71" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5316,7 +5316,7 @@
       <c r="G72" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="53" t="inlineStr">
+      <c r="H72" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5336,7 +5336,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L72" s="53" t="inlineStr">
+      <c r="L72" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5364,7 +5364,7 @@
       <c r="D73" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="67" t="inlineStr">
+      <c r="E73" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5375,7 +5375,7 @@
       <c r="G73" s="23" t="n">
         <v>97</v>
       </c>
-      <c r="H73" s="53" t="inlineStr">
+      <c r="H73" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -5395,7 +5395,7 @@
           <t>25/243</t>
         </is>
       </c>
-      <c r="L73" s="53" t="inlineStr">
+      <c r="L73" s="68" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -5434,7 +5434,7 @@
       <c r="G74" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="53" t="inlineStr">
+      <c r="H74" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5454,7 +5454,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L74" s="53" t="inlineStr">
+      <c r="L74" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5493,7 +5493,7 @@
       <c r="G75" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="53" t="inlineStr">
+      <c r="H75" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5513,7 +5513,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L75" s="53" t="inlineStr">
+      <c r="L75" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5552,7 +5552,7 @@
       <c r="G76" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H76" s="53" t="inlineStr">
+      <c r="H76" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5572,7 +5572,7 @@
           <t>0/1</t>
         </is>
       </c>
-      <c r="L76" s="53" t="inlineStr">
+      <c r="L76" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5611,7 +5611,7 @@
       <c r="G77" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="53" t="inlineStr">
+      <c r="H77" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5631,7 +5631,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L77" s="53" t="inlineStr">
+      <c r="L77" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5670,7 +5670,7 @@
       <c r="G78" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H78" s="53" t="inlineStr">
+      <c r="H78" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5690,7 +5690,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L78" s="53" t="inlineStr">
+      <c r="L78" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5718,7 +5718,7 @@
       <c r="D79" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="53" t="inlineStr">
+      <c r="E79" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -5729,7 +5729,7 @@
       <c r="G79" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H79" s="53" t="inlineStr">
+      <c r="H79" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -5749,7 +5749,7 @@
           <t>0/4</t>
         </is>
       </c>
-      <c r="L79" s="53" t="inlineStr">
+      <c r="L79" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -5788,7 +5788,7 @@
       <c r="G80" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="53" t="inlineStr">
+      <c r="H80" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5808,7 +5808,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L80" s="53" t="inlineStr">
+      <c r="L80" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -5836,7 +5836,7 @@
       <c r="D81" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="E81" s="65" t="inlineStr">
+      <c r="E81" s="53" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -5847,7 +5847,7 @@
       <c r="G81" s="23" t="n">
         <v>276</v>
       </c>
-      <c r="H81" s="67" t="inlineStr">
+      <c r="H81" s="66" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -5867,12 +5867,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L81" s="65" t="inlineStr">
+      <c r="L81" s="53" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="M81" s="65" t="inlineStr">
+      <c r="M81" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5895,7 +5895,7 @@
       <c r="D82" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E82" s="53" t="inlineStr">
+      <c r="E82" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -5906,7 +5906,7 @@
       <c r="G82" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H82" s="65" t="inlineStr">
+      <c r="H82" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -5926,7 +5926,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L82" s="65" t="inlineStr">
+      <c r="L82" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -5954,7 +5954,7 @@
       <c r="D83" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="53" t="inlineStr">
+      <c r="E83" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -5965,7 +5965,7 @@
       <c r="G83" s="23" t="n">
         <v>66</v>
       </c>
-      <c r="H83" s="53" t="inlineStr">
+      <c r="H83" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -5985,7 +5985,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L83" s="53" t="inlineStr">
+      <c r="L83" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -6013,7 +6013,7 @@
       <c r="D84" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E84" s="53" t="inlineStr">
+      <c r="E84" s="68" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
@@ -6024,7 +6024,7 @@
       <c r="G84" s="23" t="n">
         <v>136</v>
       </c>
-      <c r="H84" s="53" t="inlineStr">
+      <c r="H84" s="68" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -6044,7 +6044,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L84" s="65" t="inlineStr">
+      <c r="L84" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -6072,7 +6072,7 @@
       <c r="D85" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="E85" s="53" t="inlineStr">
+      <c r="E85" s="68" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -6083,7 +6083,7 @@
       <c r="G85" s="23" t="n">
         <v>116</v>
       </c>
-      <c r="H85" s="53" t="inlineStr">
+      <c r="H85" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -6103,7 +6103,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L85" s="65" t="inlineStr">
+      <c r="L85" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -6131,7 +6131,7 @@
       <c r="D86" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E86" s="53" t="inlineStr">
+      <c r="E86" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -6142,7 +6142,7 @@
       <c r="G86" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="H86" s="53" t="inlineStr">
+      <c r="H86" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -6162,7 +6162,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L86" s="53" t="inlineStr">
+      <c r="L86" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -6190,7 +6190,7 @@
       <c r="D87" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E87" s="67" t="inlineStr">
+      <c r="E87" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6201,7 +6201,7 @@
       <c r="G87" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="H87" s="53" t="inlineStr">
+      <c r="H87" s="68" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -6221,7 +6221,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L87" s="53" t="inlineStr">
+      <c r="L87" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -6249,7 +6249,7 @@
       <c r="D88" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="53" t="inlineStr">
+      <c r="E88" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6260,7 +6260,7 @@
       <c r="G88" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H88" s="53" t="inlineStr">
+      <c r="H88" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -6280,7 +6280,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L88" s="53" t="inlineStr">
+      <c r="L88" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -6308,7 +6308,7 @@
       <c r="D89" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E89" s="53" t="inlineStr">
+      <c r="E89" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -6319,7 +6319,7 @@
       <c r="G89" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H89" s="53" t="inlineStr">
+      <c r="H89" s="68" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -6339,7 +6339,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L89" s="53" t="inlineStr">
+      <c r="L89" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -6378,7 +6378,7 @@
       <c r="G90" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H90" s="53" t="inlineStr">
+      <c r="H90" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -6398,7 +6398,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L90" s="65" t="inlineStr">
+      <c r="L90" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -6437,7 +6437,7 @@
       <c r="G91" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H91" s="53" t="inlineStr">
+      <c r="H91" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -6457,7 +6457,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L91" s="65" t="inlineStr">
+      <c r="L91" s="53" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -6485,7 +6485,7 @@
       <c r="D92" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E92" s="53" t="inlineStr">
+      <c r="E92" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -6496,7 +6496,7 @@
       <c r="G92" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H92" s="53" t="inlineStr">
+      <c r="H92" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -6516,9 +6516,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L92" s="65" t="inlineStr">
-        <is>
-          <t>54%</t>
+      <c r="L92" s="53" t="inlineStr">
+        <is>
+          <t>55%</t>
         </is>
       </c>
       <c r="M92" s="27" t="inlineStr">
@@ -6544,7 +6544,7 @@
       <c r="D93" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="53" t="inlineStr">
+      <c r="E93" s="68" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
@@ -6553,16 +6553,16 @@
         <v>146</v>
       </c>
       <c r="G93" s="23" t="n">
-        <v>57</v>
-      </c>
-      <c r="H93" s="53" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>59</v>
+      </c>
+      <c r="H93" s="68" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="I93" s="23" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
       <c r="J93" s="23" t="inlineStr">
@@ -6575,9 +6575,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L93" s="65" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="L93" s="53" t="inlineStr">
+        <is>
+          <t>53%</t>
         </is>
       </c>
       <c r="M93" s="27" t="inlineStr">
@@ -6614,7 +6614,7 @@
       <c r="G94" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H94" s="53" t="inlineStr">
+      <c r="H94" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -6634,7 +6634,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L94" s="53" t="inlineStr">
+      <c r="L94" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -6662,7 +6662,7 @@
       <c r="D95" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E95" s="53" t="inlineStr">
+      <c r="E95" s="68" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -6673,7 +6673,7 @@
       <c r="G95" s="23" t="n">
         <v>35</v>
       </c>
-      <c r="H95" s="53" t="inlineStr">
+      <c r="H95" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -6693,7 +6693,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L95" s="65" t="inlineStr">
+      <c r="L95" s="53" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -6721,7 +6721,7 @@
       <c r="D96" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E96" s="53" t="inlineStr">
+      <c r="E96" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6732,7 +6732,7 @@
       <c r="G96" s="23" t="n">
         <v>189</v>
       </c>
-      <c r="H96" s="65" t="inlineStr">
+      <c r="H96" s="53" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -6752,7 +6752,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L96" s="65" t="inlineStr">
+      <c r="L96" s="53" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
@@ -6780,7 +6780,7 @@
       <c r="D97" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="53" t="inlineStr">
+      <c r="E97" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6791,7 +6791,7 @@
       <c r="G97" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H97" s="53" t="inlineStr">
+      <c r="H97" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -6811,7 +6811,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L97" s="53" t="inlineStr">
+      <c r="L97" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -6839,7 +6839,7 @@
       <c r="D98" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E98" s="53" t="inlineStr">
+      <c r="E98" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6850,7 +6850,7 @@
       <c r="G98" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H98" s="65" t="inlineStr">
+      <c r="H98" s="53" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -6870,7 +6870,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L98" s="65" t="inlineStr">
+      <c r="L98" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -6898,7 +6898,7 @@
       <c r="D99" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="53" t="inlineStr">
+      <c r="E99" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6909,7 +6909,7 @@
       <c r="G99" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="53" t="inlineStr">
+      <c r="H99" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -6929,7 +6929,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L99" s="53" t="inlineStr">
+      <c r="L99" s="68" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
@@ -6957,7 +6957,7 @@
       <c r="D100" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="53" t="inlineStr">
+      <c r="E100" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -6968,7 +6968,7 @@
       <c r="G100" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H100" s="53" t="inlineStr">
+      <c r="H100" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6988,7 +6988,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L100" s="53" t="inlineStr">
+      <c r="L100" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -7016,7 +7016,7 @@
       <c r="D101" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="53" t="inlineStr">
+      <c r="E101" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7027,7 +7027,7 @@
       <c r="G101" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H101" s="65" t="inlineStr">
+      <c r="H101" s="53" t="inlineStr">
         <is>
           <t>61%</t>
         </is>
@@ -7047,7 +7047,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L101" s="65" t="inlineStr">
+      <c r="L101" s="53" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
@@ -7075,7 +7075,7 @@
       <c r="D102" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E102" s="65" t="inlineStr">
+      <c r="E102" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -7086,7 +7086,7 @@
       <c r="G102" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H102" s="53" t="inlineStr">
+      <c r="H102" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7106,7 +7106,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L102" s="53" t="inlineStr">
+      <c r="L102" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -7134,7 +7134,7 @@
       <c r="D103" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="65" t="inlineStr">
+      <c r="E103" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -7145,7 +7145,7 @@
       <c r="G103" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H103" s="53" t="inlineStr">
+      <c r="H103" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7165,7 +7165,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L103" s="53" t="inlineStr">
+      <c r="L103" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -7193,7 +7193,7 @@
       <c r="D104" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="65" t="inlineStr">
+      <c r="E104" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -7204,7 +7204,7 @@
       <c r="G104" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H104" s="53" t="inlineStr">
+      <c r="H104" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -7224,7 +7224,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L104" s="53" t="inlineStr">
+      <c r="L104" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -7263,7 +7263,7 @@
       <c r="G105" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H105" s="53" t="inlineStr">
+      <c r="H105" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -7283,7 +7283,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L105" s="53" t="inlineStr">
+      <c r="L105" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -7311,7 +7311,7 @@
       <c r="D106" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="53" t="inlineStr">
+      <c r="E106" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -7320,11 +7320,11 @@
         <v>125</v>
       </c>
       <c r="G106" s="23" t="n">
-        <v>38</v>
-      </c>
-      <c r="H106" s="53" t="inlineStr">
-        <is>
-          <t>30%</t>
+        <v>39</v>
+      </c>
+      <c r="H106" s="68" t="inlineStr">
+        <is>
+          <t>31%</t>
         </is>
       </c>
       <c r="I106" s="23" t="inlineStr">
@@ -7342,7 +7342,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L106" s="53" t="inlineStr">
+      <c r="L106" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -7381,7 +7381,7 @@
       <c r="G107" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H107" s="53" t="inlineStr">
+      <c r="H107" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -7401,7 +7401,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L107" s="53" t="inlineStr">
+      <c r="L107" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7440,7 +7440,7 @@
       <c r="G108" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H108" s="53" t="inlineStr">
+      <c r="H108" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -7460,7 +7460,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L108" s="53" t="inlineStr">
+      <c r="L108" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7499,7 +7499,7 @@
       <c r="G109" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H109" s="53" t="inlineStr">
+      <c r="H109" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7519,7 +7519,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L109" s="53" t="inlineStr">
+      <c r="L109" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -7547,7 +7547,7 @@
       <c r="D110" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E110" s="65" t="inlineStr">
+      <c r="E110" s="53" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7556,11 +7556,11 @@
         <v>58</v>
       </c>
       <c r="G110" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H110" s="53" t="inlineStr">
-        <is>
-          <t>41%</t>
+        <v>25</v>
+      </c>
+      <c r="H110" s="68" t="inlineStr">
+        <is>
+          <t>43%</t>
         </is>
       </c>
       <c r="I110" s="23" t="inlineStr">
@@ -7578,7 +7578,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L110" s="65" t="inlineStr">
+      <c r="L110" s="53" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
@@ -7606,7 +7606,7 @@
       <c r="D111" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="53" t="inlineStr">
+      <c r="E111" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7617,7 +7617,7 @@
       <c r="G111" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H111" s="53" t="inlineStr">
+      <c r="H111" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -7637,7 +7637,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L111" s="53" t="inlineStr">
+      <c r="L111" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -7676,7 +7676,7 @@
       <c r="G112" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H112" s="53" t="inlineStr">
+      <c r="H112" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -7696,7 +7696,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L112" s="53" t="inlineStr">
+      <c r="L112" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -7735,7 +7735,7 @@
       <c r="G113" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="53" t="inlineStr">
+      <c r="H113" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7755,7 +7755,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L113" s="53" t="inlineStr">
+      <c r="L113" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -7792,11 +7792,11 @@
         <v>61</v>
       </c>
       <c r="G114" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="H114" s="65" t="inlineStr">
-        <is>
-          <t>66%</t>
+        <v>41</v>
+      </c>
+      <c r="H114" s="53" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="I114" s="23" t="inlineStr">
@@ -7814,7 +7814,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L114" s="65" t="inlineStr">
+      <c r="L114" s="53" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
@@ -7853,7 +7853,7 @@
       <c r="G115" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H115" s="65" t="inlineStr">
+      <c r="H115" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -7873,7 +7873,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L115" s="65" t="inlineStr">
+      <c r="L115" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -7901,7 +7901,7 @@
       <c r="D116" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="E116" s="53" t="inlineStr">
+      <c r="E116" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -7910,11 +7910,11 @@
         <v>246</v>
       </c>
       <c r="G116" s="23" t="n">
-        <v>188</v>
-      </c>
-      <c r="H116" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+        <v>189</v>
+      </c>
+      <c r="H116" s="53" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
       <c r="I116" s="23" t="inlineStr">
@@ -7932,12 +7932,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L116" s="67" t="inlineStr">
-        <is>
-          <t>98%</t>
-        </is>
-      </c>
-      <c r="M116" s="65" t="inlineStr">
+      <c r="L116" s="66" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="M116" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7960,7 +7960,7 @@
       <c r="D117" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="53" t="inlineStr">
+      <c r="E117" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -7971,7 +7971,7 @@
       <c r="G117" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="H117" s="65" t="inlineStr">
+      <c r="H117" s="53" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -7991,12 +7991,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L117" s="67" t="inlineStr">
+      <c r="L117" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M117" s="67" t="inlineStr">
+      <c r="M117" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -8019,7 +8019,7 @@
       <c r="D118" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="53" t="inlineStr">
+      <c r="E118" s="68" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -8030,7 +8030,7 @@
       <c r="G118" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="H118" s="53" t="inlineStr">
+      <c r="H118" s="68" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -8050,12 +8050,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L118" s="65" t="inlineStr">
+      <c r="L118" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
       </c>
-      <c r="M118" s="65" t="inlineStr">
+      <c r="M118" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8078,7 +8078,7 @@
       <c r="D119" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E119" s="53" t="inlineStr">
+      <c r="E119" s="68" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -8087,9 +8087,9 @@
         <v>215</v>
       </c>
       <c r="G119" s="23" t="n">
-        <v>165</v>
-      </c>
-      <c r="H119" s="65" t="inlineStr">
+        <v>166</v>
+      </c>
+      <c r="H119" s="53" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -8109,12 +8109,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L119" s="67" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="M119" s="65" t="inlineStr">
+      <c r="L119" s="66" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="M119" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8137,7 +8137,7 @@
       <c r="D120" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="53" t="inlineStr">
+      <c r="E120" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8148,7 +8148,7 @@
       <c r="G120" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H120" s="65" t="inlineStr">
+      <c r="H120" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -8168,12 +8168,12 @@
           <t>4/8</t>
         </is>
       </c>
-      <c r="L120" s="67" t="inlineStr">
+      <c r="L120" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="M120" s="65" t="inlineStr">
+      <c r="M120" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8196,7 +8196,7 @@
       <c r="D121" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="53" t="inlineStr">
+      <c r="E121" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -8207,7 +8207,7 @@
       <c r="G121" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H121" s="53" t="inlineStr">
+      <c r="H121" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -8227,7 +8227,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L121" s="65" t="inlineStr">
+      <c r="L121" s="53" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -8255,7 +8255,7 @@
       <c r="D122" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E122" s="53" t="inlineStr">
+      <c r="E122" s="68" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -8264,16 +8264,16 @@
         <v>214</v>
       </c>
       <c r="G122" s="23" t="n">
-        <v>136</v>
-      </c>
-      <c r="H122" s="65" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>146</v>
+      </c>
+      <c r="H122" s="53" t="inlineStr">
+        <is>
+          <t>68%</t>
         </is>
       </c>
       <c r="I122" s="23" t="inlineStr">
         <is>
-          <t>74/89</t>
+          <t>84/89</t>
         </is>
       </c>
       <c r="J122" s="23" t="inlineStr">
@@ -8286,9 +8286,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L122" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+      <c r="L122" s="53" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="M122" s="27" t="inlineStr">
@@ -8325,7 +8325,7 @@
       <c r="G123" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="H123" s="53" t="inlineStr">
+      <c r="H123" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="L123" s="53" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="M123" s="27" t="inlineStr">
@@ -8382,16 +8382,16 @@
         <v>35</v>
       </c>
       <c r="G124" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H124" s="53" t="inlineStr">
-        <is>
-          <t>31%</t>
+        <v>13</v>
+      </c>
+      <c r="H124" s="68" t="inlineStr">
+        <is>
+          <t>37%</t>
         </is>
       </c>
       <c r="I124" s="23" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
       <c r="J124" s="23" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="L124" s="53" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="M124" s="27" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="D125" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="E125" s="53" t="inlineStr">
+      <c r="E125" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -8441,16 +8441,16 @@
         <v>247</v>
       </c>
       <c r="G125" s="23" t="n">
-        <v>140</v>
-      </c>
-      <c r="H125" s="65" t="inlineStr">
-        <is>
-          <t>57%</t>
+        <v>154</v>
+      </c>
+      <c r="H125" s="53" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="I125" s="23" t="inlineStr">
         <is>
-          <t>71/93</t>
+          <t>85/93</t>
         </is>
       </c>
       <c r="J125" s="23" t="inlineStr">
@@ -8463,9 +8463,9 @@
           <t>6/12</t>
         </is>
       </c>
-      <c r="L125" s="65" t="inlineStr">
-        <is>
-          <t>70%</t>
+      <c r="L125" s="53" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
       <c r="M125" s="27" t="inlineStr">
@@ -8502,7 +8502,7 @@
       <c r="G126" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H126" s="53" t="inlineStr">
+      <c r="H126" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -8522,7 +8522,7 @@
           <t>4/8</t>
         </is>
       </c>
-      <c r="L126" s="53" t="inlineStr">
+      <c r="L126" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -8561,7 +8561,7 @@
       <c r="G127" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H127" s="53" t="inlineStr">
+      <c r="H127" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -8581,12 +8581,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L127" s="65" t="inlineStr">
+      <c r="L127" s="53" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
       </c>
-      <c r="M127" s="65" t="inlineStr">
+      <c r="M127" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8609,7 +8609,7 @@
       <c r="D128" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E128" s="53" t="inlineStr">
+      <c r="E128" s="68" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -8620,7 +8620,7 @@
       <c r="G128" s="23" t="n">
         <v>89</v>
       </c>
-      <c r="H128" s="53" t="inlineStr">
+      <c r="H128" s="68" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8640,7 +8640,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L128" s="65" t="inlineStr">
+      <c r="L128" s="53" t="inlineStr">
         <is>
           <t>53%</t>
         </is>
@@ -8679,7 +8679,7 @@
       <c r="G129" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="H129" s="53" t="inlineStr">
+      <c r="H129" s="68" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -8699,7 +8699,7 @@
           <t>4/8</t>
         </is>
       </c>
-      <c r="L129" s="53" t="inlineStr">
+      <c r="L129" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8738,7 +8738,7 @@
       <c r="G130" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H130" s="53" t="inlineStr">
+      <c r="H130" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -8758,7 +8758,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L130" s="53" t="inlineStr">
+      <c r="L130" s="68" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -8786,7 +8786,7 @@
       <c r="D131" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E131" s="53" t="inlineStr">
+      <c r="E131" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -8797,7 +8797,7 @@
       <c r="G131" s="23" t="n">
         <v>101</v>
       </c>
-      <c r="H131" s="53" t="inlineStr">
+      <c r="H131" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -8817,7 +8817,7 @@
           <t>6/12</t>
         </is>
       </c>
-      <c r="L131" s="65" t="inlineStr">
+      <c r="L131" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -8856,7 +8856,7 @@
       <c r="G132" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H132" s="53" t="inlineStr">
+      <c r="H132" s="68" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -8876,7 +8876,7 @@
           <t>4/8</t>
         </is>
       </c>
-      <c r="L132" s="53" t="inlineStr">
+      <c r="L132" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -8915,7 +8915,7 @@
       <c r="G133" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H133" s="53" t="inlineStr">
+      <c r="H133" s="68" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
@@ -8935,7 +8935,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L133" s="53" t="inlineStr">
+      <c r="L133" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -8963,7 +8963,7 @@
       <c r="D134" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E134" s="53" t="inlineStr">
+      <c r="E134" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -8974,7 +8974,7 @@
       <c r="G134" s="23" t="n">
         <v>86</v>
       </c>
-      <c r="H134" s="53" t="inlineStr">
+      <c r="H134" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -8994,7 +8994,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L134" s="65" t="inlineStr">
+      <c r="L134" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -9033,7 +9033,7 @@
       <c r="G135" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="H135" s="53" t="inlineStr">
+      <c r="H135" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -9053,7 +9053,7 @@
           <t>3/6</t>
         </is>
       </c>
-      <c r="L135" s="53" t="inlineStr">
+      <c r="L135" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -9092,7 +9092,7 @@
       <c r="G136" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H136" s="53" t="inlineStr">
+      <c r="H136" s="68" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -9112,7 +9112,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L136" s="53" t="inlineStr">
+      <c r="L136" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -9140,7 +9140,7 @@
       <c r="D137" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E137" s="53" t="inlineStr">
+      <c r="E137" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9151,7 +9151,7 @@
       <c r="G137" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="H137" s="53" t="inlineStr">
+      <c r="H137" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -9171,7 +9171,7 @@
           <t>6/12</t>
         </is>
       </c>
-      <c r="L137" s="65" t="inlineStr">
+      <c r="L137" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -9199,7 +9199,7 @@
       <c r="D138" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="53" t="inlineStr">
+      <c r="E138" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -9210,7 +9210,7 @@
       <c r="G138" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H138" s="65" t="inlineStr">
+      <c r="H138" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -9230,9 +9230,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L138" s="65" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="L138" s="53" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="M138" s="27" t="inlineStr">
@@ -9258,7 +9258,7 @@
       <c r="D139" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E139" s="53" t="inlineStr">
+      <c r="E139" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -9267,11 +9267,11 @@
         <v>73</v>
       </c>
       <c r="G139" s="23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H139" s="65" t="inlineStr">
-        <is>
-          <t>81%</t>
+        <v>60</v>
+      </c>
+      <c r="H139" s="53" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
       <c r="I139" s="23" t="inlineStr">
@@ -9289,9 +9289,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L139" s="65" t="inlineStr">
-        <is>
-          <t>87%</t>
+      <c r="L139" s="66" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="M139" s="27" t="inlineStr">
@@ -9317,7 +9317,7 @@
       <c r="D140" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E140" s="53" t="inlineStr">
+      <c r="E140" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -9326,11 +9326,11 @@
         <v>68</v>
       </c>
       <c r="G140" s="23" t="n">
-        <v>53</v>
-      </c>
-      <c r="H140" s="65" t="inlineStr">
-        <is>
-          <t>78%</t>
+        <v>54</v>
+      </c>
+      <c r="H140" s="53" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="I140" s="23" t="inlineStr">
@@ -9348,9 +9348,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L140" s="65" t="inlineStr">
-        <is>
-          <t>86%</t>
+      <c r="L140" s="53" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="M140" s="27" t="inlineStr">
@@ -9376,7 +9376,7 @@
       <c r="D141" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E141" s="53" t="inlineStr">
+      <c r="E141" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9387,7 +9387,7 @@
       <c r="G141" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H141" s="65" t="inlineStr">
+      <c r="H141" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -9407,12 +9407,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L141" s="67" t="inlineStr">
+      <c r="L141" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M141" s="67" t="inlineStr">
+      <c r="M141" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -9435,7 +9435,7 @@
       <c r="D142" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="53" t="inlineStr">
+      <c r="E142" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -9444,11 +9444,11 @@
         <v>42</v>
       </c>
       <c r="G142" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="H142" s="65" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>28</v>
+      </c>
+      <c r="H142" s="53" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="I142" s="23" t="inlineStr">
@@ -9466,12 +9466,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L142" s="67" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-      <c r="M142" s="65" t="inlineStr">
+      <c r="L142" s="66" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M142" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -9494,7 +9494,7 @@
       <c r="D143" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E143" s="53" t="inlineStr">
+      <c r="E143" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -9505,7 +9505,7 @@
       <c r="G143" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="H143" s="65" t="inlineStr">
+      <c r="H143" s="53" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -9525,12 +9525,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L143" s="67" t="inlineStr">
+      <c r="L143" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="M143" s="65" t="inlineStr">
+      <c r="M143" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -9553,7 +9553,7 @@
       <c r="D144" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E144" s="65" t="inlineStr">
+      <c r="E144" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -9564,7 +9564,7 @@
       <c r="G144" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H144" s="65" t="inlineStr">
+      <c r="H144" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -9584,12 +9584,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L144" s="67" t="inlineStr">
+      <c r="L144" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
       </c>
-      <c r="M144" s="65" t="inlineStr">
+      <c r="M144" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -9612,7 +9612,7 @@
       <c r="D145" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="65" t="inlineStr">
+      <c r="E145" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -9623,7 +9623,7 @@
       <c r="G145" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H145" s="65" t="inlineStr">
+      <c r="H145" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -9643,7 +9643,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L145" s="67" t="inlineStr">
+      <c r="L145" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -9671,7 +9671,7 @@
       <c r="D146" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E146" s="65" t="inlineStr">
+      <c r="E146" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -9682,7 +9682,7 @@
       <c r="G146" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H146" s="65" t="inlineStr">
+      <c r="H146" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -9702,7 +9702,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L146" s="67" t="inlineStr">
+      <c r="L146" s="66" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -9730,7 +9730,7 @@
       <c r="D147" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E147" s="65" t="inlineStr">
+      <c r="E147" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -9741,7 +9741,7 @@
       <c r="G147" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H147" s="53" t="inlineStr">
+      <c r="H147" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -9761,7 +9761,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L147" s="53" t="inlineStr">
+      <c r="L147" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -9789,7 +9789,7 @@
       <c r="D148" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E148" s="65" t="inlineStr">
+      <c r="E148" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -9800,7 +9800,7 @@
       <c r="G148" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="H148" s="53" t="inlineStr">
+      <c r="H148" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -9820,7 +9820,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L148" s="53" t="inlineStr">
+      <c r="L148" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -9848,7 +9848,7 @@
       <c r="D149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E149" s="53" t="inlineStr">
+      <c r="E149" s="68" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -9859,7 +9859,7 @@
       <c r="G149" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H149" s="53" t="inlineStr">
+      <c r="H149" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -9879,7 +9879,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L149" s="65" t="inlineStr">
+      <c r="L149" s="53" t="inlineStr">
         <is>
           <t>54%</t>
         </is>
@@ -9907,7 +9907,7 @@
       <c r="D150" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E150" s="53" t="inlineStr">
+      <c r="E150" s="68" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -9918,7 +9918,7 @@
       <c r="G150" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H150" s="65" t="inlineStr">
+      <c r="H150" s="53" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -9938,12 +9938,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L150" s="67" t="inlineStr">
+      <c r="L150" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M150" s="67" t="inlineStr">
+      <c r="M150" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -9966,7 +9966,7 @@
       <c r="D151" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E151" s="53" t="inlineStr">
+      <c r="E151" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -9977,7 +9977,7 @@
       <c r="G151" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="H151" s="65" t="inlineStr">
+      <c r="H151" s="53" t="inlineStr">
         <is>
           <t>86%</t>
         </is>
@@ -9997,12 +9997,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L151" s="67" t="inlineStr">
+      <c r="L151" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M151" s="67" t="inlineStr">
+      <c r="M151" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -10025,7 +10025,7 @@
       <c r="D152" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E152" s="65" t="inlineStr">
+      <c r="E152" s="53" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -10034,16 +10034,16 @@
         <v>43</v>
       </c>
       <c r="G152" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="H152" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+        <v>34</v>
+      </c>
+      <c r="H152" s="53" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="I152" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="J152" s="23" t="inlineStr">
@@ -10056,9 +10056,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L152" s="65" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="L152" s="66" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="M152" s="27" t="inlineStr">
@@ -10084,7 +10084,7 @@
       <c r="D153" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E153" s="65" t="inlineStr">
+      <c r="E153" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -10093,16 +10093,16 @@
         <v>43</v>
       </c>
       <c r="G153" s="23" t="n">
-        <v>31</v>
-      </c>
-      <c r="H153" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+        <v>34</v>
+      </c>
+      <c r="H153" s="53" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="I153" s="23" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="J153" s="23" t="inlineStr">
@@ -10115,9 +10115,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L153" s="65" t="inlineStr">
-        <is>
-          <t>85%</t>
+      <c r="L153" s="66" t="inlineStr">
+        <is>
+          <t>97%</t>
         </is>
       </c>
       <c r="M153" s="27" t="inlineStr">
@@ -10143,7 +10143,7 @@
       <c r="D154" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E154" s="53" t="inlineStr">
+      <c r="E154" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -10154,7 +10154,7 @@
       <c r="G154" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H154" s="65" t="inlineStr">
+      <c r="H154" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -10174,9 +10174,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L154" s="65" t="inlineStr">
-        <is>
-          <t>61%</t>
+      <c r="L154" s="53" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="M154" s="27" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="D155" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E155" s="65" t="inlineStr">
+      <c r="E155" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -10213,7 +10213,7 @@
       <c r="G155" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H155" s="53" t="inlineStr">
+      <c r="H155" s="68" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
@@ -10233,9 +10233,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L155" s="65" t="inlineStr">
-        <is>
-          <t>59%</t>
+      <c r="L155" s="53" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="M155" s="27" t="inlineStr">
@@ -10261,7 +10261,7 @@
       <c r="D156" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E156" s="65" t="inlineStr">
+      <c r="E156" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -10272,7 +10272,7 @@
       <c r="G156" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H156" s="53" t="inlineStr">
+      <c r="H156" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -10292,7 +10292,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L156" s="65" t="inlineStr">
+      <c r="L156" s="53" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -10320,7 +10320,7 @@
       <c r="D157" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E157" s="53" t="inlineStr">
+      <c r="E157" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -10331,7 +10331,7 @@
       <c r="G157" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H157" s="65" t="inlineStr">
+      <c r="H157" s="53" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10351,12 +10351,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L157" s="67" t="inlineStr">
+      <c r="L157" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M157" s="67" t="inlineStr">
+      <c r="M157" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -10379,7 +10379,7 @@
       <c r="D158" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E158" s="53" t="inlineStr">
+      <c r="E158" s="68" t="inlineStr">
         <is>
           <t>42%</t>
         </is>
@@ -10390,7 +10390,7 @@
       <c r="G158" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H158" s="67" t="inlineStr">
+      <c r="H158" s="66" t="inlineStr">
         <is>
           <t>91%</t>
         </is>
@@ -10410,12 +10410,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L158" s="67" t="inlineStr">
+      <c r="L158" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M158" s="67" t="inlineStr">
+      <c r="M158" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -10438,7 +10438,7 @@
       <c r="D159" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E159" s="65" t="inlineStr">
+      <c r="E159" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -10449,7 +10449,7 @@
       <c r="G159" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="H159" s="65" t="inlineStr">
+      <c r="H159" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10469,7 +10469,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L159" s="65" t="inlineStr">
+      <c r="L159" s="53" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10497,7 +10497,7 @@
       <c r="D160" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E160" s="53" t="inlineStr">
+      <c r="E160" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -10508,7 +10508,7 @@
       <c r="G160" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="H160" s="65" t="inlineStr">
+      <c r="H160" s="53" t="inlineStr">
         <is>
           <t>71%</t>
         </is>
@@ -10528,7 +10528,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L160" s="65" t="inlineStr">
+      <c r="L160" s="53" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -10556,7 +10556,7 @@
       <c r="D161" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E161" s="53" t="inlineStr">
+      <c r="E161" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -10567,7 +10567,7 @@
       <c r="G161" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H161" s="65" t="inlineStr">
+      <c r="H161" s="53" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -10587,7 +10587,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L161" s="65" t="inlineStr">
+      <c r="L161" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10615,7 +10615,7 @@
       <c r="D162" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="53" t="inlineStr">
+      <c r="E162" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10626,7 +10626,7 @@
       <c r="G162" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H162" s="65" t="inlineStr">
+      <c r="H162" s="53" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -10646,7 +10646,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L162" s="65" t="inlineStr">
+      <c r="L162" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -10674,7 +10674,7 @@
       <c r="D163" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E163" s="53" t="inlineStr">
+      <c r="E163" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10685,7 +10685,7 @@
       <c r="G163" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H163" s="65" t="inlineStr">
+      <c r="H163" s="53" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
@@ -10705,7 +10705,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L163" s="65" t="inlineStr">
+      <c r="L163" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -10733,7 +10733,7 @@
       <c r="D164" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="E164" s="53" t="inlineStr">
+      <c r="E164" s="68" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -10742,11 +10742,11 @@
         <v>44</v>
       </c>
       <c r="G164" s="23" t="n">
-        <v>36</v>
-      </c>
-      <c r="H164" s="65" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>37</v>
+      </c>
+      <c r="H164" s="53" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="I164" s="23" t="inlineStr">
@@ -10764,12 +10764,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L164" s="67" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="M164" s="65" t="inlineStr">
+      <c r="L164" s="66" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="M164" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -10792,7 +10792,7 @@
       <c r="D165" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E165" s="53" t="inlineStr">
+      <c r="E165" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -10801,11 +10801,11 @@
         <v>44</v>
       </c>
       <c r="G165" s="23" t="n">
-        <v>33</v>
-      </c>
-      <c r="H165" s="65" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>34</v>
+      </c>
+      <c r="H165" s="53" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
       <c r="I165" s="23" t="inlineStr">
@@ -10823,12 +10823,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L165" s="67" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="M165" s="65" t="inlineStr">
+      <c r="L165" s="66" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="M165" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -10851,7 +10851,7 @@
       <c r="D166" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E166" s="65" t="inlineStr">
+      <c r="E166" s="53" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
@@ -10860,16 +10860,16 @@
         <v>44</v>
       </c>
       <c r="G166" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H166" s="65" t="inlineStr">
-        <is>
-          <t>68%</t>
+        <v>31</v>
+      </c>
+      <c r="H166" s="53" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="I166" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="J166" s="23" t="inlineStr">
@@ -10882,9 +10882,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L166" s="65" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="L166" s="53" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
       <c r="M166" s="27" t="inlineStr">
@@ -10910,7 +10910,7 @@
       <c r="D167" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E167" s="53" t="inlineStr">
+      <c r="E167" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -10919,16 +10919,16 @@
         <v>44</v>
       </c>
       <c r="G167" s="23" t="n">
-        <v>26</v>
-      </c>
-      <c r="H167" s="65" t="inlineStr">
-        <is>
-          <t>59%</t>
+        <v>27</v>
+      </c>
+      <c r="H167" s="53" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
       <c r="I167" s="23" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="J167" s="23" t="inlineStr">
@@ -10941,9 +10941,9 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L167" s="65" t="inlineStr">
-        <is>
-          <t>74%</t>
+      <c r="L167" s="53" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
       <c r="M167" s="27" t="inlineStr">
@@ -10969,7 +10969,7 @@
       <c r="D168" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E168" s="53" t="inlineStr">
+      <c r="E168" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -10980,7 +10980,7 @@
       <c r="G168" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H168" s="53" t="inlineStr">
+      <c r="H168" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -11000,9 +11000,9 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L168" s="65" t="inlineStr">
-        <is>
-          <t>57%</t>
+      <c r="L168" s="53" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="M168" s="27" t="inlineStr">
@@ -11028,7 +11028,7 @@
       <c r="D169" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="53" t="inlineStr">
+      <c r="E169" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -11039,7 +11039,7 @@
       <c r="G169" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H169" s="53" t="inlineStr">
+      <c r="H169" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -11059,9 +11059,9 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L169" s="65" t="inlineStr">
-        <is>
-          <t>57%</t>
+      <c r="L169" s="53" t="inlineStr">
+        <is>
+          <t>60%</t>
         </is>
       </c>
       <c r="M169" s="27" t="inlineStr">
@@ -11087,7 +11087,7 @@
       <c r="D170" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E170" s="67" t="inlineStr">
+      <c r="E170" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11098,7 +11098,7 @@
       <c r="G170" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H170" s="53" t="inlineStr">
+      <c r="H170" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11118,7 +11118,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L170" s="65" t="inlineStr">
+      <c r="L170" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -11146,7 +11146,7 @@
       <c r="D171" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E171" s="53" t="inlineStr">
+      <c r="E171" s="68" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
@@ -11155,11 +11155,11 @@
         <v>76</v>
       </c>
       <c r="G171" s="23" t="n">
-        <v>62</v>
-      </c>
-      <c r="H171" s="65" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>63</v>
+      </c>
+      <c r="H171" s="53" t="inlineStr">
+        <is>
+          <t>83%</t>
         </is>
       </c>
       <c r="I171" s="23" t="inlineStr">
@@ -11177,12 +11177,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L171" s="67" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="M171" s="65" t="inlineStr">
+      <c r="L171" s="66" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="M171" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11205,7 +11205,7 @@
       <c r="D172" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E172" s="53" t="inlineStr">
+      <c r="E172" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11216,7 +11216,7 @@
       <c r="G172" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="H172" s="65" t="inlineStr">
+      <c r="H172" s="53" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -11236,12 +11236,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L172" s="65" t="inlineStr">
+      <c r="L172" s="53" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="M172" s="65" t="inlineStr">
+      <c r="M172" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11264,7 +11264,7 @@
       <c r="D173" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="53" t="inlineStr">
+      <c r="E173" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -11273,11 +11273,11 @@
         <v>73</v>
       </c>
       <c r="G173" s="23" t="n">
-        <v>63</v>
-      </c>
-      <c r="H173" s="65" t="inlineStr">
-        <is>
-          <t>86%</t>
+        <v>64</v>
+      </c>
+      <c r="H173" s="53" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I173" s="23" t="inlineStr">
@@ -11295,12 +11295,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L173" s="67" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="M173" s="65" t="inlineStr">
+      <c r="L173" s="66" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="M173" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11323,7 +11323,7 @@
       <c r="D174" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E174" s="53" t="inlineStr">
+      <c r="E174" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -11334,7 +11334,7 @@
       <c r="G174" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H174" s="65" t="inlineStr">
+      <c r="H174" s="53" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -11354,12 +11354,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L174" s="65" t="inlineStr">
+      <c r="L174" s="53" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="M174" s="65" t="inlineStr">
+      <c r="M174" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11382,7 +11382,7 @@
       <c r="D175" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="53" t="inlineStr">
+      <c r="E175" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -11391,16 +11391,16 @@
         <v>73</v>
       </c>
       <c r="G175" s="23" t="n">
-        <v>47</v>
-      </c>
-      <c r="H175" s="65" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>59</v>
+      </c>
+      <c r="H175" s="53" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
       <c r="I175" s="23" t="inlineStr">
         <is>
-          <t>24/38</t>
+          <t>36/38</t>
         </is>
       </c>
       <c r="J175" s="23" t="inlineStr">
@@ -11413,9 +11413,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L175" s="65" t="inlineStr">
-        <is>
-          <t>67%</t>
+      <c r="L175" s="53" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="M175" s="27" t="inlineStr">
@@ -11450,16 +11450,16 @@
         <v>41</v>
       </c>
       <c r="G176" s="23" t="n">
-        <v>25</v>
-      </c>
-      <c r="H176" s="65" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>26</v>
+      </c>
+      <c r="H176" s="53" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
       <c r="I176" s="23" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J176" s="23" t="inlineStr">
@@ -11472,7 +11472,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L176" s="65" t="inlineStr">
+      <c r="L176" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -11500,7 +11500,7 @@
       <c r="D177" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="53" t="inlineStr">
+      <c r="E177" s="68" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
@@ -11509,16 +11509,16 @@
         <v>73</v>
       </c>
       <c r="G177" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="H177" s="65" t="inlineStr">
-        <is>
-          <t>60%</t>
+        <v>53</v>
+      </c>
+      <c r="H177" s="53" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="I177" s="23" t="inlineStr">
         <is>
-          <t>23/38</t>
+          <t>32/38</t>
         </is>
       </c>
       <c r="J177" s="23" t="inlineStr">
@@ -11531,7 +11531,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L177" s="65" t="inlineStr">
+      <c r="L177" s="53" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -11568,16 +11568,16 @@
         <v>41</v>
       </c>
       <c r="G178" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="H178" s="53" t="inlineStr">
-        <is>
-          <t>32%</t>
+        <v>16</v>
+      </c>
+      <c r="H178" s="68" t="inlineStr">
+        <is>
+          <t>39%</t>
         </is>
       </c>
       <c r="I178" s="23" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="J178" s="23" t="inlineStr">
@@ -11590,7 +11590,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L178" s="53" t="inlineStr">
+      <c r="L178" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -11618,7 +11618,7 @@
       <c r="D179" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E179" s="53" t="inlineStr">
+      <c r="E179" s="68" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -11629,7 +11629,7 @@
       <c r="G179" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H179" s="53" t="inlineStr">
+      <c r="H179" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -11649,9 +11649,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L179" s="53" t="inlineStr">
-        <is>
-          <t>43%</t>
+      <c r="L179" s="68" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="M179" s="27" t="inlineStr">
@@ -11688,7 +11688,7 @@
       <c r="G180" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H180" s="53" t="inlineStr">
+      <c r="H180" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -11708,7 +11708,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L180" s="53" t="inlineStr">
+      <c r="L180" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11736,7 +11736,7 @@
       <c r="D181" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E181" s="53" t="inlineStr">
+      <c r="E181" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -11747,7 +11747,7 @@
       <c r="G181" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H181" s="53" t="inlineStr">
+      <c r="H181" s="68" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -11767,9 +11767,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L181" s="53" t="inlineStr">
-        <is>
-          <t>39%</t>
+      <c r="L181" s="68" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="M181" s="27" t="inlineStr">
@@ -11806,7 +11806,7 @@
       <c r="G182" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H182" s="53" t="inlineStr">
+      <c r="H182" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -11826,7 +11826,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L182" s="53" t="inlineStr">
+      <c r="L182" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11854,7 +11854,7 @@
       <c r="D183" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E183" s="53" t="inlineStr">
+      <c r="E183" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -11865,7 +11865,7 @@
       <c r="G183" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H183" s="53" t="inlineStr">
+      <c r="H183" s="68" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
@@ -11885,7 +11885,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L183" s="53" t="inlineStr">
+      <c r="L183" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -11924,7 +11924,7 @@
       <c r="G184" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H184" s="53" t="inlineStr">
+      <c r="H184" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -11944,7 +11944,7 @@
           <t>0/2</t>
         </is>
       </c>
-      <c r="L184" s="53" t="inlineStr">
+      <c r="L184" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -11972,7 +11972,7 @@
       <c r="D185" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="E185" s="53" t="inlineStr">
+      <c r="E185" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -11981,11 +11981,11 @@
         <v>90</v>
       </c>
       <c r="G185" s="23" t="n">
-        <v>69</v>
-      </c>
-      <c r="H185" s="65" t="inlineStr">
-        <is>
-          <t>77%</t>
+        <v>70</v>
+      </c>
+      <c r="H185" s="53" t="inlineStr">
+        <is>
+          <t>78%</t>
         </is>
       </c>
       <c r="I185" s="23" t="inlineStr">
@@ -12003,12 +12003,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L185" s="67" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="M185" s="65" t="inlineStr">
+      <c r="L185" s="66" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M185" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -12031,7 +12031,7 @@
       <c r="D186" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E186" s="65" t="inlineStr">
+      <c r="E186" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -12040,11 +12040,11 @@
         <v>78</v>
       </c>
       <c r="G186" s="23" t="n">
-        <v>69</v>
-      </c>
-      <c r="H186" s="65" t="inlineStr">
-        <is>
-          <t>88%</t>
+        <v>70</v>
+      </c>
+      <c r="H186" s="66" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="I186" s="23" t="inlineStr">
@@ -12062,12 +12062,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L186" s="67" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="M186" s="65" t="inlineStr">
+      <c r="L186" s="66" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="M186" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -12090,7 +12090,7 @@
       <c r="D187" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="E187" s="65" t="inlineStr">
+      <c r="E187" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -12099,11 +12099,11 @@
         <v>78</v>
       </c>
       <c r="G187" s="23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H187" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+        <v>67</v>
+      </c>
+      <c r="H187" s="53" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I187" s="23" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="J187" s="23" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="K187" s="23" t="inlineStr">
@@ -12121,9 +12121,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L187" s="65" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="L187" s="66" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="M187" s="27" t="inlineStr">
@@ -12149,7 +12149,7 @@
       <c r="D188" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E188" s="53" t="inlineStr">
+      <c r="E188" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -12158,11 +12158,11 @@
         <v>78</v>
       </c>
       <c r="G188" s="23" t="n">
-        <v>59</v>
-      </c>
-      <c r="H188" s="65" t="inlineStr">
-        <is>
-          <t>76%</t>
+        <v>67</v>
+      </c>
+      <c r="H188" s="53" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="I188" s="23" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="J188" s="23" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>16/16</t>
         </is>
       </c>
       <c r="K188" s="23" t="inlineStr">
@@ -12180,9 +12180,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L188" s="65" t="inlineStr">
-        <is>
-          <t>83%</t>
+      <c r="L188" s="66" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="M188" s="27" t="inlineStr">
@@ -12208,7 +12208,7 @@
       <c r="D189" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E189" s="53" t="inlineStr">
+      <c r="E189" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -12219,7 +12219,7 @@
       <c r="G189" s="23" t="n">
         <v>47</v>
       </c>
-      <c r="H189" s="65" t="inlineStr">
+      <c r="H189" s="53" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -12239,9 +12239,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L189" s="65" t="inlineStr">
-        <is>
-          <t>66%</t>
+      <c r="L189" s="53" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="M189" s="27" t="inlineStr">
@@ -12267,7 +12267,7 @@
       <c r="D190" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E190" s="53" t="inlineStr">
+      <c r="E190" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -12278,7 +12278,7 @@
       <c r="G190" s="23" t="n">
         <v>46</v>
       </c>
-      <c r="H190" s="65" t="inlineStr">
+      <c r="H190" s="53" t="inlineStr">
         <is>
           <t>59%</t>
         </is>
@@ -12298,9 +12298,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L190" s="65" t="inlineStr">
-        <is>
-          <t>64%</t>
+      <c r="L190" s="53" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="M190" s="27" t="inlineStr">
@@ -12326,7 +12326,7 @@
       <c r="D191" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E191" s="53" t="inlineStr">
+      <c r="E191" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -12337,7 +12337,7 @@
       <c r="G191" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="H191" s="53" t="inlineStr">
+      <c r="H191" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -12357,9 +12357,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L191" s="53" t="inlineStr">
-        <is>
-          <t>44%</t>
+      <c r="L191" s="68" t="inlineStr">
+        <is>
+          <t>46%</t>
         </is>
       </c>
       <c r="M191" s="27" t="inlineStr">
@@ -12385,7 +12385,7 @@
       <c r="D192" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="E192" s="53" t="inlineStr">
+      <c r="E192" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -12396,7 +12396,7 @@
       <c r="G192" s="23" t="n">
         <v>256</v>
       </c>
-      <c r="H192" s="65" t="inlineStr">
+      <c r="H192" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -12416,9 +12416,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L192" s="65" t="inlineStr">
-        <is>
-          <t>67%</t>
+      <c r="L192" s="53" t="inlineStr">
+        <is>
+          <t>72%</t>
         </is>
       </c>
       <c r="M192" s="27" t="inlineStr">
@@ -12444,7 +12444,7 @@
       <c r="D193" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E193" s="53" t="inlineStr">
+      <c r="E193" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12455,7 +12455,7 @@
       <c r="G193" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="H193" s="53" t="inlineStr">
+      <c r="H193" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -12475,7 +12475,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L193" s="53" t="inlineStr">
+      <c r="L193" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -12503,7 +12503,7 @@
       <c r="D194" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E194" s="53" t="inlineStr">
+      <c r="E194" s="68" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
@@ -12514,7 +12514,7 @@
       <c r="G194" s="23" t="n">
         <v>37</v>
       </c>
-      <c r="H194" s="53" t="inlineStr">
+      <c r="H194" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -12534,7 +12534,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L194" s="53" t="inlineStr">
+      <c r="L194" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -12573,7 +12573,7 @@
       <c r="G195" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H195" s="53" t="inlineStr">
+      <c r="H195" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12593,7 +12593,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L195" s="53" t="inlineStr">
+      <c r="L195" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12621,7 +12621,7 @@
       <c r="D196" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="E196" s="67" t="inlineStr">
+      <c r="E196" s="66" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -12632,7 +12632,7 @@
       <c r="G196" s="23" t="n">
         <v>115</v>
       </c>
-      <c r="H196" s="65" t="inlineStr">
+      <c r="H196" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -12652,12 +12652,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L196" s="67" t="inlineStr">
+      <c r="L196" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M196" s="67" t="inlineStr">
+      <c r="M196" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
@@ -12680,7 +12680,7 @@
       <c r="D197" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="E197" s="67" t="inlineStr">
+      <c r="E197" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -12691,7 +12691,7 @@
       <c r="G197" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H197" s="53" t="inlineStr">
+      <c r="H197" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -12711,7 +12711,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L197" s="65" t="inlineStr">
+      <c r="L197" s="53" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -12739,7 +12739,7 @@
       <c r="D198" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="53" t="inlineStr">
+      <c r="E198" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12750,7 +12750,7 @@
       <c r="G198" s="23" t="n">
         <v>271</v>
       </c>
-      <c r="H198" s="65" t="inlineStr">
+      <c r="H198" s="53" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -12770,7 +12770,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L198" s="67" t="inlineStr">
+      <c r="L198" s="66" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
@@ -12798,7 +12798,7 @@
       <c r="D199" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="E199" s="65" t="inlineStr">
+      <c r="E199" s="53" t="inlineStr">
         <is>
           <t>57%</t>
         </is>
@@ -12809,7 +12809,7 @@
       <c r="G199" s="23" t="n">
         <v>157</v>
       </c>
-      <c r="H199" s="65" t="inlineStr">
+      <c r="H199" s="53" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
@@ -12829,7 +12829,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L199" s="53" t="inlineStr">
+      <c r="L199" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -12868,7 +12868,7 @@
       <c r="G200" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="53" t="inlineStr">
+      <c r="H200" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -12888,7 +12888,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L200" s="53" t="inlineStr">
+      <c r="L200" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -12927,7 +12927,7 @@
       <c r="G201" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H201" s="53" t="inlineStr">
+      <c r="H201" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -12947,7 +12947,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L201" s="53" t="inlineStr">
+      <c r="L201" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -12986,7 +12986,7 @@
       <c r="G202" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H202" s="53" t="inlineStr">
+      <c r="H202" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13006,7 +13006,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L202" s="53" t="inlineStr">
+      <c r="L202" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -13045,7 +13045,7 @@
       <c r="G203" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H203" s="53" t="inlineStr">
+      <c r="H203" s="68" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -13065,7 +13065,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L203" s="53" t="inlineStr">
+      <c r="L203" s="68" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -13104,7 +13104,7 @@
       <c r="G204" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H204" s="53" t="inlineStr">
+      <c r="H204" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13124,7 +13124,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L204" s="53" t="inlineStr">
+      <c r="L204" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13163,7 +13163,7 @@
       <c r="G205" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H205" s="53" t="inlineStr">
+      <c r="H205" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13183,7 +13183,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L205" s="53" t="inlineStr">
+      <c r="L205" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13211,7 +13211,7 @@
       <c r="D206" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E206" s="67" t="inlineStr">
+      <c r="E206" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13222,7 +13222,7 @@
       <c r="G206" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="53" t="inlineStr">
+      <c r="H206" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -13242,7 +13242,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L206" s="53" t="inlineStr">
+      <c r="L206" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -13270,7 +13270,7 @@
       <c r="D207" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E207" s="67" t="inlineStr">
+      <c r="E207" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -13281,7 +13281,7 @@
       <c r="G207" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H207" s="53" t="inlineStr">
+      <c r="H207" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -13301,7 +13301,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L207" s="53" t="inlineStr">
+      <c r="L207" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -13340,7 +13340,7 @@
       <c r="G208" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H208" s="53" t="inlineStr">
+      <c r="H208" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -13360,7 +13360,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L208" s="53" t="inlineStr">
+      <c r="L208" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -13399,7 +13399,7 @@
       <c r="G209" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H209" s="53" t="inlineStr">
+      <c r="H209" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -13419,7 +13419,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L209" s="53" t="inlineStr">
+      <c r="L209" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -13458,7 +13458,7 @@
       <c r="G210" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="53" t="inlineStr">
+      <c r="H210" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13478,7 +13478,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L210" s="53" t="inlineStr">
+      <c r="L210" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13517,7 +13517,7 @@
       <c r="G211" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H211" s="53" t="inlineStr">
+      <c r="H211" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -13537,7 +13537,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L211" s="53" t="inlineStr">
+      <c r="L211" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -13565,7 +13565,7 @@
       <c r="D212" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E212" s="53" t="inlineStr">
+      <c r="E212" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13576,7 +13576,7 @@
       <c r="G212" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H212" s="53" t="inlineStr">
+      <c r="H212" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -13596,7 +13596,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L212" s="53" t="inlineStr">
+      <c r="L212" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -13635,7 +13635,7 @@
       <c r="G213" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H213" s="53" t="inlineStr">
+      <c r="H213" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -13655,7 +13655,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L213" s="53" t="inlineStr">
+      <c r="L213" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -13683,7 +13683,7 @@
       <c r="D214" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E214" s="53" t="inlineStr">
+      <c r="E214" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13694,7 +13694,7 @@
       <c r="G214" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="H214" s="53" t="inlineStr">
+      <c r="H214" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -13714,7 +13714,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L214" s="53" t="inlineStr">
+      <c r="L214" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -13742,7 +13742,7 @@
       <c r="D215" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E215" s="53" t="inlineStr">
+      <c r="E215" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13753,7 +13753,7 @@
       <c r="G215" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H215" s="53" t="inlineStr">
+      <c r="H215" s="68" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -13773,7 +13773,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L215" s="53" t="inlineStr">
+      <c r="L215" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -13812,7 +13812,7 @@
       <c r="G216" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H216" s="53" t="inlineStr">
+      <c r="H216" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -13832,7 +13832,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L216" s="53" t="inlineStr">
+      <c r="L216" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -13871,7 +13871,7 @@
       <c r="G217" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="H217" s="65" t="inlineStr">
+      <c r="H217" s="53" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13891,7 +13891,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L217" s="65" t="inlineStr">
+      <c r="L217" s="53" t="inlineStr">
         <is>
           <t>73%</t>
         </is>
@@ -13919,7 +13919,7 @@
       <c r="D218" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E218" s="53" t="inlineStr">
+      <c r="E218" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -13930,7 +13930,7 @@
       <c r="G218" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H218" s="65" t="inlineStr">
+      <c r="H218" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13950,7 +13950,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L218" s="65" t="inlineStr">
+      <c r="L218" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -13989,7 +13989,7 @@
       <c r="G219" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H219" s="53" t="inlineStr">
+      <c r="H219" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14009,7 +14009,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L219" s="53" t="inlineStr">
+      <c r="L219" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -14048,7 +14048,7 @@
       <c r="G220" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="53" t="inlineStr">
+      <c r="H220" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14068,7 +14068,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L220" s="53" t="inlineStr">
+      <c r="L220" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14107,7 +14107,7 @@
       <c r="G221" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H221" s="53" t="inlineStr">
+      <c r="H221" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14127,7 +14127,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L221" s="53" t="inlineStr">
+      <c r="L221" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14166,7 +14166,7 @@
       <c r="G222" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H222" s="53" t="inlineStr">
+      <c r="H222" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14186,7 +14186,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L222" s="53" t="inlineStr">
+      <c r="L222" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14225,7 +14225,7 @@
       <c r="G223" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H223" s="53" t="inlineStr">
+      <c r="H223" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14245,7 +14245,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L223" s="53" t="inlineStr">
+      <c r="L223" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14284,7 +14284,7 @@
       <c r="G224" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H224" s="53" t="inlineStr">
+      <c r="H224" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14304,7 +14304,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L224" s="53" t="inlineStr">
+      <c r="L224" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14343,7 +14343,7 @@
       <c r="G225" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H225" s="53" t="inlineStr">
+      <c r="H225" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14363,7 +14363,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L225" s="53" t="inlineStr">
+      <c r="L225" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14391,7 +14391,7 @@
       <c r="D226" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E226" s="53" t="inlineStr">
+      <c r="E226" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14402,7 +14402,7 @@
       <c r="G226" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H226" s="53" t="inlineStr">
+      <c r="H226" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -14422,7 +14422,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L226" s="53" t="inlineStr">
+      <c r="L226" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -14461,7 +14461,7 @@
       <c r="G227" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H227" s="53" t="inlineStr">
+      <c r="H227" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14481,7 +14481,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L227" s="53" t="inlineStr">
+      <c r="L227" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14520,7 +14520,7 @@
       <c r="G228" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="53" t="inlineStr">
+      <c r="H228" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -14540,12 +14540,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L228" s="65" t="inlineStr">
+      <c r="L228" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="M228" s="65" t="inlineStr">
+      <c r="M228" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -14568,7 +14568,7 @@
       <c r="D229" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E229" s="53" t="inlineStr">
+      <c r="E229" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -14579,7 +14579,7 @@
       <c r="G229" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="H229" s="67" t="inlineStr">
+      <c r="H229" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14599,7 +14599,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L229" s="67" t="inlineStr">
+      <c r="L229" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -14638,7 +14638,7 @@
       <c r="G230" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="53" t="inlineStr">
+      <c r="H230" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14658,7 +14658,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L230" s="53" t="inlineStr">
+      <c r="L230" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14697,7 +14697,7 @@
       <c r="G231" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="53" t="inlineStr">
+      <c r="H231" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14717,7 +14717,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L231" s="53" t="inlineStr">
+      <c r="L231" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14756,7 +14756,7 @@
       <c r="G232" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H232" s="53" t="inlineStr">
+      <c r="H232" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14776,7 +14776,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L232" s="53" t="inlineStr">
+      <c r="L232" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -14804,7 +14804,7 @@
       <c r="D233" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E233" s="53" t="inlineStr">
+      <c r="E233" s="68" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
@@ -14815,7 +14815,7 @@
       <c r="G233" s="23" t="n">
         <v>57</v>
       </c>
-      <c r="H233" s="53" t="inlineStr">
+      <c r="H233" s="68" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
@@ -14835,7 +14835,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L233" s="53" t="inlineStr">
+      <c r="L233" s="68" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -14863,7 +14863,7 @@
       <c r="D234" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E234" s="53" t="inlineStr">
+      <c r="E234" s="68" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -14874,7 +14874,7 @@
       <c r="G234" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="H234" s="53" t="inlineStr">
+      <c r="H234" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -14894,7 +14894,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L234" s="53" t="inlineStr">
+      <c r="L234" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -14933,7 +14933,7 @@
       <c r="G235" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H235" s="53" t="inlineStr">
+      <c r="H235" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -14953,7 +14953,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L235" s="53" t="inlineStr">
+      <c r="L235" s="68" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -14981,7 +14981,7 @@
       <c r="D236" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E236" s="65" t="inlineStr">
+      <c r="E236" s="53" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
@@ -14992,7 +14992,7 @@
       <c r="G236" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="H236" s="53" t="inlineStr">
+      <c r="H236" s="68" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15012,7 +15012,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L236" s="53" t="inlineStr">
+      <c r="L236" s="68" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
@@ -15040,7 +15040,7 @@
       <c r="D237" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E237" s="53" t="inlineStr">
+      <c r="E237" s="68" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
@@ -15051,7 +15051,7 @@
       <c r="G237" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="H237" s="53" t="inlineStr">
+      <c r="H237" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15071,7 +15071,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L237" s="53" t="inlineStr">
+      <c r="L237" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -15099,7 +15099,7 @@
       <c r="D238" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E238" s="53" t="inlineStr">
+      <c r="E238" s="68" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -15110,7 +15110,7 @@
       <c r="G238" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H238" s="53" t="inlineStr">
+      <c r="H238" s="68" t="inlineStr">
         <is>
           <t>43%</t>
         </is>
@@ -15130,7 +15130,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L238" s="53" t="inlineStr">
+      <c r="L238" s="68" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
@@ -15158,7 +15158,7 @@
       <c r="D239" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E239" s="53" t="inlineStr">
+      <c r="E239" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15167,11 +15167,11 @@
         <v>138</v>
       </c>
       <c r="G239" s="23" t="n">
-        <v>24</v>
-      </c>
-      <c r="H239" s="53" t="inlineStr">
-        <is>
-          <t>17%</t>
+        <v>25</v>
+      </c>
+      <c r="H239" s="68" t="inlineStr">
+        <is>
+          <t>18%</t>
         </is>
       </c>
       <c r="I239" s="23" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="J239" s="23" t="inlineStr">
         <is>
-          <t>16/44</t>
+          <t>17/44</t>
         </is>
       </c>
       <c r="K239" s="23" t="inlineStr">
@@ -15189,7 +15189,7 @@
           <t>2/4</t>
         </is>
       </c>
-      <c r="L239" s="53" t="inlineStr">
+      <c r="L239" s="68" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -15217,7 +15217,7 @@
       <c r="D240" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E240" s="53" t="inlineStr">
+      <c r="E240" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -15228,7 +15228,7 @@
       <c r="G240" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="H240" s="65" t="inlineStr">
+      <c r="H240" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -15248,9 +15248,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L240" s="65" t="inlineStr">
-        <is>
-          <t>70%</t>
+      <c r="L240" s="53" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
       <c r="M240" s="27" t="inlineStr">
@@ -15276,7 +15276,7 @@
       <c r="D241" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E241" s="53" t="inlineStr">
+      <c r="E241" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15287,7 +15287,7 @@
       <c r="G241" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="H241" s="65" t="inlineStr">
+      <c r="H241" s="53" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -15307,12 +15307,12 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L241" s="67" t="inlineStr">
+      <c r="L241" s="66" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="M241" s="65" t="inlineStr">
+      <c r="M241" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -15335,7 +15335,7 @@
       <c r="D242" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="E242" s="65" t="inlineStr">
+      <c r="E242" s="53" t="inlineStr">
         <is>
           <t>82%</t>
         </is>
@@ -15346,7 +15346,7 @@
       <c r="G242" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="H242" s="53" t="inlineStr">
+      <c r="H242" s="68" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15366,7 +15366,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L242" s="53" t="inlineStr">
+      <c r="L242" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -15394,7 +15394,7 @@
       <c r="D243" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E243" s="53" t="inlineStr">
+      <c r="E243" s="68" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -15405,7 +15405,7 @@
       <c r="G243" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="H243" s="53" t="inlineStr">
+      <c r="H243" s="68" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
@@ -15425,7 +15425,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L243" s="53" t="inlineStr">
+      <c r="L243" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -15453,7 +15453,7 @@
       <c r="D244" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E244" s="53" t="inlineStr">
+      <c r="E244" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -15464,7 +15464,7 @@
       <c r="G244" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H244" s="53" t="inlineStr">
+      <c r="H244" s="68" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
@@ -15484,7 +15484,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L244" s="53" t="inlineStr">
+      <c r="L244" s="68" t="inlineStr">
         <is>
           <t>44%</t>
         </is>
@@ -15512,7 +15512,7 @@
       <c r="D245" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E245" s="53" t="inlineStr">
+      <c r="E245" s="68" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -15523,7 +15523,7 @@
       <c r="G245" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="H245" s="53" t="inlineStr">
+      <c r="H245" s="68" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -15543,7 +15543,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L245" s="65" t="inlineStr">
+      <c r="L245" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -15571,7 +15571,7 @@
       <c r="D246" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E246" s="53" t="inlineStr">
+      <c r="E246" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15582,7 +15582,7 @@
       <c r="G246" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H246" s="53" t="inlineStr">
+      <c r="H246" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -15602,7 +15602,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L246" s="53" t="inlineStr">
+      <c r="L246" s="68" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -15630,7 +15630,7 @@
       <c r="D247" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E247" s="53" t="inlineStr">
+      <c r="E247" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15641,7 +15641,7 @@
       <c r="G247" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H247" s="53" t="inlineStr">
+      <c r="H247" s="68" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
@@ -15661,7 +15661,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L247" s="65" t="inlineStr">
+      <c r="L247" s="53" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
@@ -15689,7 +15689,7 @@
       <c r="D248" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E248" s="53" t="inlineStr">
+      <c r="E248" s="68" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -15700,7 +15700,7 @@
       <c r="G248" s="23" t="n">
         <v>34</v>
       </c>
-      <c r="H248" s="53" t="inlineStr">
+      <c r="H248" s="68" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
@@ -15720,7 +15720,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L248" s="65" t="inlineStr">
+      <c r="L248" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -15748,7 +15748,7 @@
       <c r="D249" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E249" s="53" t="inlineStr">
+      <c r="E249" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -15759,7 +15759,7 @@
       <c r="G249" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="H249" s="53" t="inlineStr">
+      <c r="H249" s="68" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
@@ -15779,7 +15779,7 @@
           <t>1/4</t>
         </is>
       </c>
-      <c r="L249" s="53" t="inlineStr">
+      <c r="L249" s="68" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
@@ -15807,7 +15807,7 @@
       <c r="D250" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="E250" s="53" t="inlineStr">
+      <c r="E250" s="68" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
@@ -15816,11 +15816,11 @@
         <v>67</v>
       </c>
       <c r="G250" s="23" t="n">
-        <v>46</v>
-      </c>
-      <c r="H250" s="65" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>47</v>
+      </c>
+      <c r="H250" s="53" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
       <c r="I250" s="23" t="inlineStr">
@@ -15838,9 +15838,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L250" s="65" t="inlineStr">
-        <is>
-          <t>84%</t>
+      <c r="L250" s="53" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="M250" s="27" t="inlineStr">
@@ -15866,7 +15866,7 @@
       <c r="D251" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E251" s="53" t="inlineStr">
+      <c r="E251" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -15875,11 +15875,11 @@
         <v>79</v>
       </c>
       <c r="G251" s="23" t="n">
-        <v>52</v>
-      </c>
-      <c r="H251" s="65" t="inlineStr">
-        <is>
-          <t>66%</t>
+        <v>53</v>
+      </c>
+      <c r="H251" s="53" t="inlineStr">
+        <is>
+          <t>67%</t>
         </is>
       </c>
       <c r="I251" s="23" t="inlineStr">
@@ -15897,9 +15897,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L251" s="65" t="inlineStr">
-        <is>
-          <t>84%</t>
+      <c r="L251" s="53" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="M251" s="27" t="inlineStr">
@@ -15925,7 +15925,7 @@
       <c r="D252" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="E252" s="53" t="inlineStr">
+      <c r="E252" s="68" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
@@ -15934,11 +15934,11 @@
         <v>90</v>
       </c>
       <c r="G252" s="23" t="n">
-        <v>65</v>
-      </c>
-      <c r="H252" s="65" t="inlineStr">
-        <is>
-          <t>72%</t>
+        <v>66</v>
+      </c>
+      <c r="H252" s="53" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="I252" s="23" t="inlineStr">
@@ -15956,9 +15956,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L252" s="67" t="inlineStr">
-        <is>
-          <t>98%</t>
+      <c r="L252" s="66" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="M252" s="27" t="inlineStr">
@@ -15984,7 +15984,7 @@
       <c r="D253" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E253" s="53" t="inlineStr">
+      <c r="E253" s="68" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
@@ -15995,7 +15995,7 @@
       <c r="G253" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="H253" s="65" t="inlineStr">
+      <c r="H253" s="53" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
@@ -16015,7 +16015,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L253" s="65" t="inlineStr">
+      <c r="L253" s="53" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
@@ -16043,7 +16043,7 @@
       <c r="D254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="53" t="inlineStr">
+      <c r="E254" s="68" t="inlineStr">
         <is>
           <t>21%</t>
         </is>
@@ -16054,7 +16054,7 @@
       <c r="G254" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H254" s="53" t="inlineStr">
+      <c r="H254" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -16074,7 +16074,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L254" s="53" t="inlineStr">
+      <c r="L254" s="68" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
@@ -16102,7 +16102,7 @@
       <c r="D255" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="E255" s="67" t="inlineStr">
+      <c r="E255" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -16113,7 +16113,7 @@
       <c r="G255" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H255" s="53" t="inlineStr">
+      <c r="H255" s="68" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
@@ -16133,7 +16133,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L255" s="53" t="inlineStr">
+      <c r="L255" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -16161,7 +16161,7 @@
       <c r="D256" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E256" s="53" t="inlineStr">
+      <c r="E256" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -16172,7 +16172,7 @@
       <c r="G256" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H256" s="53" t="inlineStr">
+      <c r="H256" s="68" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -16192,7 +16192,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L256" s="65" t="inlineStr">
+      <c r="L256" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -16231,7 +16231,7 @@
       <c r="G257" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H257" s="53" t="inlineStr">
+      <c r="H257" s="68" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
@@ -16251,9 +16251,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L257" s="53" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="L257" s="68" t="inlineStr">
+        <is>
+          <t>31%</t>
         </is>
       </c>
       <c r="M257" s="27" t="inlineStr">
@@ -16288,11 +16288,11 @@
         <v>58</v>
       </c>
       <c r="G258" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H258" s="53" t="inlineStr">
-        <is>
-          <t>10%</t>
+        <v>7</v>
+      </c>
+      <c r="H258" s="68" t="inlineStr">
+        <is>
+          <t>12%</t>
         </is>
       </c>
       <c r="I258" s="23" t="inlineStr">
@@ -16310,7 +16310,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L258" s="53" t="inlineStr">
+      <c r="L258" s="68" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -16338,7 +16338,7 @@
       <c r="D259" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E259" s="53" t="inlineStr">
+      <c r="E259" s="68" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
@@ -16349,7 +16349,7 @@
       <c r="G259" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="H259" s="53" t="inlineStr">
+      <c r="H259" s="68" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
@@ -16369,9 +16369,9 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L259" s="53" t="inlineStr">
-        <is>
-          <t>42%</t>
+      <c r="L259" s="68" t="inlineStr">
+        <is>
+          <t>46%</t>
         </is>
       </c>
       <c r="M259" s="27" t="inlineStr">
@@ -16397,7 +16397,7 @@
       <c r="D260" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E260" s="53" t="inlineStr">
+      <c r="E260" s="68" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
@@ -16408,7 +16408,7 @@
       <c r="G260" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="H260" s="53" t="inlineStr">
+      <c r="H260" s="68" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
@@ -16428,7 +16428,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L260" s="53" t="inlineStr">
+      <c r="L260" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -16456,7 +16456,7 @@
       <c r="D261" s="23" t="n">
         <v>70</v>
       </c>
-      <c r="E261" s="65" t="inlineStr">
+      <c r="E261" s="53" t="inlineStr">
         <is>
           <t>74%</t>
         </is>
@@ -16467,7 +16467,7 @@
       <c r="G261" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="H261" s="65" t="inlineStr">
+      <c r="H261" s="53" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
@@ -16487,12 +16487,12 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L261" s="65" t="inlineStr">
+      <c r="L261" s="53" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="M261" s="65" t="inlineStr">
+      <c r="M261" s="53" t="inlineStr">
         <is>
           <t>PARTIAL(05-03-2026)</t>
         </is>
@@ -16526,7 +16526,7 @@
       <c r="G262" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H262" s="53" t="inlineStr">
+      <c r="H262" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16546,7 +16546,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L262" s="53" t="inlineStr">
+      <c r="L262" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16585,7 +16585,7 @@
       <c r="G263" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H263" s="53" t="inlineStr">
+      <c r="H263" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16605,7 +16605,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L263" s="53" t="inlineStr">
+      <c r="L263" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16644,7 +16644,7 @@
       <c r="G264" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H264" s="53" t="inlineStr">
+      <c r="H264" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16664,7 +16664,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L264" s="53" t="inlineStr">
+      <c r="L264" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16703,7 +16703,7 @@
       <c r="G265" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H265" s="53" t="inlineStr">
+      <c r="H265" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16723,7 +16723,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L265" s="53" t="inlineStr">
+      <c r="L265" s="68" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
@@ -16762,7 +16762,7 @@
       <c r="G266" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H266" s="53" t="inlineStr">
+      <c r="H266" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16782,7 +16782,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L266" s="53" t="inlineStr">
+      <c r="L266" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16821,7 +16821,7 @@
       <c r="G267" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H267" s="53" t="inlineStr">
+      <c r="H267" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16841,7 +16841,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L267" s="53" t="inlineStr">
+      <c r="L267" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16880,7 +16880,7 @@
       <c r="G268" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H268" s="53" t="inlineStr">
+      <c r="H268" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16900,7 +16900,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L268" s="53" t="inlineStr">
+      <c r="L268" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16939,7 +16939,7 @@
       <c r="G269" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H269" s="53" t="inlineStr">
+      <c r="H269" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -16959,7 +16959,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L269" s="53" t="inlineStr">
+      <c r="L269" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -16998,7 +16998,7 @@
       <c r="G270" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H270" s="53" t="inlineStr">
+      <c r="H270" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -17018,7 +17018,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L270" s="53" t="inlineStr">
+      <c r="L270" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -17057,7 +17057,7 @@
       <c r="G271" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H271" s="53" t="inlineStr">
+      <c r="H271" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -17077,7 +17077,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L271" s="53" t="inlineStr">
+      <c r="L271" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -17116,7 +17116,7 @@
       <c r="G272" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="H272" s="53" t="inlineStr">
+      <c r="H272" s="68" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
@@ -17136,7 +17136,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L272" s="53" t="inlineStr">
+      <c r="L272" s="68" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
@@ -17175,7 +17175,7 @@
       <c r="G273" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H273" s="53" t="inlineStr">
+      <c r="H273" s="68" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -17195,7 +17195,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L273" s="53" t="inlineStr">
+      <c r="L273" s="68" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
@@ -17234,7 +17234,7 @@
       <c r="G274" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="H274" s="65" t="inlineStr">
+      <c r="H274" s="53" t="inlineStr">
         <is>
           <t>58%</t>
         </is>
@@ -17254,7 +17254,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L274" s="65" t="inlineStr">
+      <c r="L274" s="53" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -17282,7 +17282,7 @@
       <c r="D275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E275" s="53" t="inlineStr">
+      <c r="E275" s="68" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
@@ -17293,7 +17293,7 @@
       <c r="G275" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="53" t="inlineStr">
+      <c r="H275" s="68" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -17313,7 +17313,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L275" s="53" t="inlineStr">
+      <c r="L275" s="68" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
@@ -17352,7 +17352,7 @@
       <c r="G276" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H276" s="53" t="inlineStr">
+      <c r="H276" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17372,7 +17372,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L276" s="53" t="inlineStr">
+      <c r="L276" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17411,7 +17411,7 @@
       <c r="G277" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="H277" s="53" t="inlineStr">
+      <c r="H277" s="68" t="inlineStr">
         <is>
           <t>36%</t>
         </is>
@@ -17431,7 +17431,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L277" s="65" t="inlineStr">
+      <c r="L277" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17470,7 +17470,7 @@
       <c r="G278" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H278" s="53" t="inlineStr">
+      <c r="H278" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17490,7 +17490,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L278" s="53" t="inlineStr">
+      <c r="L278" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17529,7 +17529,7 @@
       <c r="G279" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H279" s="53" t="inlineStr">
+      <c r="H279" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17549,7 +17549,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L279" s="53" t="inlineStr">
+      <c r="L279" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17588,7 +17588,7 @@
       <c r="G280" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H280" s="53" t="inlineStr">
+      <c r="H280" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17608,7 +17608,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L280" s="53" t="inlineStr">
+      <c r="L280" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17636,7 +17636,7 @@
       <c r="D281" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="E281" s="65" t="inlineStr">
+      <c r="E281" s="53" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -17647,7 +17647,7 @@
       <c r="G281" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="H281" s="65" t="inlineStr">
+      <c r="H281" s="53" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -17667,7 +17667,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L281" s="65" t="inlineStr">
+      <c r="L281" s="53" t="inlineStr">
         <is>
           <t>67%</t>
         </is>
@@ -17706,7 +17706,7 @@
       <c r="G282" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H282" s="53" t="inlineStr">
+      <c r="H282" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17726,7 +17726,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L282" s="53" t="inlineStr">
+      <c r="L282" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17765,7 +17765,7 @@
       <c r="G283" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H283" s="53" t="inlineStr">
+      <c r="H283" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17785,7 +17785,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L283" s="53" t="inlineStr">
+      <c r="L283" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17824,7 +17824,7 @@
       <c r="G284" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H284" s="53" t="inlineStr">
+      <c r="H284" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17844,7 +17844,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L284" s="53" t="inlineStr">
+      <c r="L284" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17883,7 +17883,7 @@
       <c r="G285" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H285" s="53" t="inlineStr">
+      <c r="H285" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17903,7 +17903,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L285" s="53" t="inlineStr">
+      <c r="L285" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -17931,7 +17931,7 @@
       <c r="D286" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="E286" s="53" t="inlineStr">
+      <c r="E286" s="68" t="inlineStr">
         <is>
           <t>18%</t>
         </is>
@@ -17942,7 +17942,7 @@
       <c r="G286" s="23" t="n">
         <v>151</v>
       </c>
-      <c r="H286" s="65" t="inlineStr">
+      <c r="H286" s="53" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
@@ -17962,14 +17962,14 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L286" s="67" t="inlineStr">
+      <c r="L286" s="66" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="M286" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
+      <c r="M286" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18001,7 +18001,7 @@
       <c r="G287" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H287" s="53" t="inlineStr">
+      <c r="H287" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18021,7 +18021,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L287" s="53" t="inlineStr">
+      <c r="L287" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18060,7 +18060,7 @@
       <c r="G288" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H288" s="53" t="inlineStr">
+      <c r="H288" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18080,7 +18080,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L288" s="53" t="inlineStr">
+      <c r="L288" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18119,7 +18119,7 @@
       <c r="G289" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="53" t="inlineStr">
+      <c r="H289" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18139,7 +18139,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L289" s="53" t="inlineStr">
+      <c r="L289" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18178,7 +18178,7 @@
       <c r="G290" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="53" t="inlineStr">
+      <c r="H290" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18198,7 +18198,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L290" s="53" t="inlineStr">
+      <c r="L290" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18237,7 +18237,7 @@
       <c r="G291" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H291" s="53" t="inlineStr">
+      <c r="H291" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18257,7 +18257,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L291" s="53" t="inlineStr">
+      <c r="L291" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18296,7 +18296,7 @@
       <c r="G292" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H292" s="53" t="inlineStr">
+      <c r="H292" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -18316,7 +18316,7 @@
           <t>0/0</t>
         </is>
       </c>
-      <c r="L292" s="53" t="inlineStr">
+      <c r="L292" s="68" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
